--- a/ORCL.xlsx
+++ b/ORCL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0021465B-E1B5-4C08-BF3E-7B36ADDC5BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECFF4CA-ECA2-4455-B2B1-47C4480B8834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50300" yWindow="3270" windowWidth="23470" windowHeight="16810" tabRatio="319" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" tabRatio="319" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     Q125 guidance: DD revenue growth</t>
       </text>
     </comment>
-    <comment ref="V78" authorId="2" shapeId="0" xr:uid="{DF3A69DD-1198-42A5-A83A-5484CF412A11}">
+    <comment ref="V80" authorId="2" shapeId="0" xr:uid="{DF3A69DD-1198-42A5-A83A-5484CF412A11}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="130">
   <si>
     <t>Price</t>
   </si>
@@ -173,9 +173,6 @@
     <t>Cloud Services</t>
   </si>
   <si>
-    <t>Cloud License</t>
-  </si>
-  <si>
     <t>Hardware</t>
   </si>
   <si>
@@ -371,9 +368,6 @@
     <t>FQ425</t>
   </si>
   <si>
-    <t xml:space="preserve">  License Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Cloud Services</t>
   </si>
   <si>
@@ -453,6 +447,18 @@
   </si>
   <si>
     <t>Q325</t>
+  </si>
+  <si>
+    <t>Software License</t>
+  </si>
+  <si>
+    <t>Software Support</t>
+  </si>
+  <si>
+    <t>Lease ROU</t>
+  </si>
+  <si>
+    <t>Lease</t>
   </si>
 </sst>
 </file>
@@ -600,16 +606,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>48022</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>41672</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>43657</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>48022</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>7938</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>41672</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>123031</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -624,8 +630,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17704991" y="43657"/>
-          <a:ext cx="0" cy="13950156"/>
+          <a:off x="19618722" y="0"/>
+          <a:ext cx="0" cy="13629481"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -658,7 +664,7 @@
     <xdr:to>
       <xdr:col>47</xdr:col>
       <xdr:colOff>19255</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>38307</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1010,7 +1016,7 @@
   <threadedComment ref="AU34" dT="2024-09-11T18:29:26.52" personId="{7216FEC0-B7FB-466B-9D42-622825855BC7}" id="{A4A66BCC-1D5A-42FB-AF87-0976A774FC6D}">
     <text>Q125 guidance: DD revenue growth</text>
   </threadedComment>
-  <threadedComment ref="V78" dT="2024-09-11T18:53:29.19" personId="{7216FEC0-B7FB-466B-9D42-622825855BC7}" id="{DF3A69DD-1198-42A5-A83A-5484CF412A11}">
+  <threadedComment ref="V80" dT="2024-09-11T18:53:29.19" personId="{7216FEC0-B7FB-466B-9D42-622825855BC7}" id="{DF3A69DD-1198-42A5-A83A-5484CF412A11}">
     <text>Didn’t add up?</text>
   </threadedComment>
 </ThreadedComments>
@@ -1028,18 +1034,18 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="2">
-        <v>262</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>1</v>
@@ -1048,19 +1054,19 @@
         <v>2909</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="3">
         <f>G3*G2</f>
-        <v>762158</v>
+        <v>436350</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
@@ -1071,12 +1077,12 @@
         <v>11005</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>4</v>
@@ -1085,24 +1091,24 @@
         <v>91315</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G7" s="3">
         <f>G4-G5+G6</f>
-        <v>842468</v>
+        <v>516660</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{284BEAAF-34CF-A143-8837-7F659B2590CD}">
-  <dimension ref="A1:EK81"/>
+  <dimension ref="A1:EK83"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" style="1" bestFit="1" customWidth="1"/>
@@ -1218,12 +1224,10 @@
         <v>45991</v>
       </c>
       <c r="AC2" s="12">
-        <f t="shared" si="1"/>
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="AD2" s="12">
-        <f t="shared" si="1"/>
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="AE2" s="12">
         <f t="shared" si="1"/>
@@ -1235,11 +1239,11 @@
       </c>
       <c r="AG2" s="12">
         <f t="shared" si="1"/>
-        <v>46445</v>
+        <v>46446</v>
       </c>
       <c r="AH2" s="12">
         <f t="shared" si="1"/>
-        <v>46537</v>
+        <v>46538</v>
       </c>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
@@ -1298,16 +1302,16 @@
     </row>
     <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>13</v>
@@ -1334,76 +1338,76 @@
         <v>14</v>
       </c>
       <c r="O3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="S3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="U3" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="V3" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="W3" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X3" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="Y3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z3" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="AA3" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AC3" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AD3" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AE3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AF3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AG3" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AH3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AG3" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH3" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="AM3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AN3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AP3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AQ3" s="4" t="s">
         <v>30</v>
@@ -1412,33 +1416,33 @@
         <v>31</v>
       </c>
       <c r="AS3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT3" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AU3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AU3" s="4" t="s">
+      <c r="AV3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AV3" s="4" t="s">
+      <c r="AW3" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AW3" s="4" t="s">
+      <c r="AX3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AX3" s="4" t="s">
+      <c r="AY3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AY3" s="4" t="s">
+      <c r="AZ3" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="AZ3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="U4" s="5">
         <v>80000</v>
@@ -1484,7 +1488,7 @@
     </row>
     <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P6" s="4">
         <v>600</v>
@@ -1522,7 +1526,7 @@
     </row>
     <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P7" s="4">
         <v>600</v>
@@ -1558,7 +1562,7 @@
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="O8" s="5">
         <v>2700</v>
@@ -1600,32 +1604,29 @@
         <v>3839</v>
       </c>
       <c r="AB8" s="5">
-        <f t="shared" ref="AB8:AH8" si="5">+X8*1.05</f>
-        <v>3678.15</v>
+        <v>3898</v>
       </c>
       <c r="AC8" s="5">
-        <f t="shared" si="5"/>
-        <v>3735.9</v>
+        <v>4026</v>
       </c>
       <c r="AD8" s="5">
-        <f t="shared" si="5"/>
-        <v>3929.1000000000004</v>
+        <v>4126</v>
       </c>
       <c r="AE8" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="AE8:AH8" si="5">+AA8*1.05</f>
         <v>4030.9500000000003</v>
       </c>
       <c r="AF8" s="5">
         <f t="shared" si="5"/>
-        <v>3862.0575000000003</v>
+        <v>4092.9</v>
       </c>
       <c r="AG8" s="5">
         <f t="shared" si="5"/>
-        <v>3922.6950000000002</v>
+        <v>4227.3</v>
       </c>
       <c r="AH8" s="5">
         <f t="shared" si="5"/>
-        <v>4125.5550000000003</v>
+        <v>4332.3</v>
       </c>
       <c r="AN8" s="4"/>
       <c r="AS8" s="5">
@@ -1642,11 +1643,11 @@
       </c>
       <c r="AV8" s="5">
         <f>SUM(AA8:AD8)</f>
-        <v>15182.15</v>
+        <v>15889</v>
       </c>
       <c r="AW8" s="5">
         <f>SUM(AE8:AH8)</f>
-        <v>15941.257500000002</v>
+        <v>16683.45</v>
       </c>
       <c r="AX8" s="4"/>
       <c r="AY8" s="4"/>
@@ -1654,7 +1655,7 @@
     </row>
     <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O9" s="5">
         <v>900</v>
@@ -1696,29 +1697,29 @@
         <v>3347</v>
       </c>
       <c r="AB9" s="5">
-        <v>4000</v>
+        <v>4079</v>
       </c>
       <c r="AC9" s="5">
-        <v>5000</v>
+        <v>4888</v>
       </c>
       <c r="AD9" s="5">
-        <v>6000</v>
+        <v>5787</v>
       </c>
       <c r="AE9" s="5">
         <f>+AD9+1000</f>
-        <v>7000</v>
+        <v>6787</v>
       </c>
       <c r="AF9" s="5">
         <f>+AE9+1000</f>
-        <v>8000</v>
+        <v>7787</v>
       </c>
       <c r="AG9" s="5">
         <f>+AF9+1000</f>
-        <v>9000</v>
+        <v>8787</v>
       </c>
       <c r="AH9" s="5">
         <f>+AG9+1000</f>
-        <v>10000</v>
+        <v>9787</v>
       </c>
       <c r="AN9" s="4"/>
       <c r="AS9" s="5">
@@ -1735,11 +1736,11 @@
       </c>
       <c r="AV9" s="5">
         <f t="shared" ref="AV9:AV16" si="6">SUM(AA9:AD9)</f>
-        <v>18347</v>
+        <v>18101</v>
       </c>
       <c r="AW9" s="5">
         <f t="shared" ref="AW9" si="7">SUM(AE9:AH9)</f>
-        <v>34000</v>
+        <v>33148</v>
       </c>
       <c r="AX9" s="5">
         <v>73000</v>
@@ -1764,7 +1765,7 @@
     </row>
     <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="O11" s="5">
         <v>3579</v>
@@ -1807,36 +1808,36 @@
         <v>6737</v>
       </c>
       <c r="AA11" s="5">
-        <f>+AA9+AA8</f>
+        <f t="shared" ref="AA11:AD11" si="8">+AA9+AA8</f>
         <v>7186</v>
       </c>
       <c r="AB11" s="5">
-        <f t="shared" ref="AB11:AH11" si="8">+AB9+AB8</f>
-        <v>7678.15</v>
+        <f t="shared" si="8"/>
+        <v>7977</v>
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="8"/>
-        <v>8735.9</v>
+        <v>8914</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="8"/>
-        <v>9929.1</v>
+        <v>9913</v>
       </c>
       <c r="AE11" s="5">
-        <f t="shared" si="8"/>
-        <v>11030.95</v>
+        <f t="shared" ref="AE11:AH11" si="9">+AE9+AE8</f>
+        <v>10817.95</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" si="8"/>
-        <v>11862.057500000001</v>
+        <f t="shared" si="9"/>
+        <v>11879.9</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="8"/>
-        <v>12922.695</v>
+        <f t="shared" si="9"/>
+        <v>13014.3</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="8"/>
-        <v>14125.555</v>
+        <f t="shared" si="9"/>
+        <v>14119.3</v>
       </c>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
@@ -1847,16 +1848,16 @@
         <v>15882</v>
       </c>
       <c r="AT11" s="5">
-        <f t="shared" ref="AT11:AT16" si="9">SUM(S11:V11)</f>
+        <f t="shared" ref="AT11:AT16" si="10">SUM(S11:V11)</f>
         <v>19775</v>
       </c>
       <c r="AU11" s="5">
-        <f t="shared" ref="AU11:AU16" si="10">SUM(W11:Z11)</f>
+        <f t="shared" ref="AU11:AU16" si="11">SUM(W11:Z11)</f>
         <v>24507</v>
       </c>
       <c r="AV11" s="5">
         <f t="shared" si="6"/>
-        <v>33529.15</v>
+        <v>33990</v>
       </c>
       <c r="AW11" s="4"/>
       <c r="AX11" s="4"/>
@@ -1865,7 +1866,7 @@
     </row>
     <row r="12" spans="1:52" s="16" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -1919,32 +1920,29 @@
         <v>4955</v>
       </c>
       <c r="AB12" s="18">
-        <f>+X12</f>
-        <v>4869</v>
+        <v>4938</v>
       </c>
       <c r="AC12" s="18">
-        <f t="shared" ref="AC12:AH12" si="11">+Y12</f>
-        <v>4797</v>
+        <v>4969</v>
       </c>
       <c r="AD12" s="18">
-        <f t="shared" si="11"/>
-        <v>4961</v>
+        <v>4943</v>
       </c>
       <c r="AE12" s="18">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AE12:AH12" si="12">+AA12</f>
         <v>4955</v>
       </c>
       <c r="AF12" s="18">
-        <f t="shared" si="11"/>
-        <v>4869</v>
+        <f t="shared" si="12"/>
+        <v>4938</v>
       </c>
       <c r="AG12" s="18">
-        <f t="shared" si="11"/>
-        <v>4797</v>
+        <f t="shared" si="12"/>
+        <v>4969</v>
       </c>
       <c r="AH12" s="18">
-        <f t="shared" si="11"/>
-        <v>4961</v>
+        <f t="shared" si="12"/>
+        <v>4943</v>
       </c>
       <c r="AI12" s="18"/>
       <c r="AJ12" s="18"/>
@@ -1961,16 +1959,16 @@
         <v>19426</v>
       </c>
       <c r="AT12" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>19608</v>
       </c>
       <c r="AU12" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>19523</v>
       </c>
       <c r="AV12" s="5">
         <f t="shared" si="6"/>
-        <v>19582</v>
+        <v>19805</v>
       </c>
       <c r="AW12" s="17"/>
       <c r="AX12" s="17"/>
@@ -2010,15 +2008,15 @@
         <v>7612</v>
       </c>
       <c r="O13" s="5">
-        <f t="shared" ref="O13:P13" si="12">+O12+O11</f>
+        <f t="shared" ref="O13:P13" si="13">+O12+O11</f>
         <v>8417</v>
       </c>
       <c r="P13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>8598</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" ref="Q13" si="13">+Q12+Q11</f>
+        <f t="shared" ref="Q13" si="14">+Q12+Q11</f>
         <v>8923</v>
       </c>
       <c r="R13" s="5">
@@ -2026,65 +2024,68 @@
         <v>9370</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" ref="S13" si="14">+S12+S11</f>
+        <f t="shared" ref="S13" si="15">+S12+S11</f>
         <v>9547</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" ref="T13" si="15">+T12+T11</f>
+        <f t="shared" ref="T13" si="16">+T12+T11</f>
         <v>9639</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" ref="U13" si="16">+U12+U11</f>
+        <f t="shared" ref="U13" si="17">+U12+U11</f>
         <v>9963</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" ref="V13" si="17">+V12+V11</f>
+        <f t="shared" ref="V13:AB13" si="18">+V11+V12</f>
         <v>10234</v>
       </c>
       <c r="W13" s="5">
+        <f t="shared" si="18"/>
         <v>10519</v>
       </c>
       <c r="X13" s="5">
+        <f t="shared" si="18"/>
         <v>10806</v>
       </c>
       <c r="Y13" s="5">
+        <f t="shared" si="18"/>
         <v>11007</v>
       </c>
       <c r="Z13" s="5">
-        <f>+Z11+Z12</f>
+        <f t="shared" si="18"/>
         <v>11698</v>
       </c>
       <c r="AA13" s="5">
-        <f>+AA11+AA12</f>
+        <f t="shared" si="18"/>
         <v>12141</v>
       </c>
       <c r="AB13" s="5">
-        <f t="shared" ref="AB13:AH13" si="18">+AB11+AB12</f>
-        <v>12547.15</v>
+        <f t="shared" ref="AB13:AH13" si="19">+AB11+AB12</f>
+        <v>12915</v>
       </c>
       <c r="AC13" s="5">
-        <f t="shared" si="18"/>
-        <v>13532.9</v>
+        <f t="shared" si="19"/>
+        <v>13883</v>
       </c>
       <c r="AD13" s="5">
-        <f t="shared" si="18"/>
-        <v>14890.1</v>
+        <f t="shared" si="19"/>
+        <v>14856</v>
       </c>
       <c r="AE13" s="5">
-        <f t="shared" si="18"/>
-        <v>15985.95</v>
+        <f t="shared" si="19"/>
+        <v>15772.95</v>
       </c>
       <c r="AF13" s="5">
-        <f t="shared" si="18"/>
-        <v>16731.057500000003</v>
+        <f t="shared" si="19"/>
+        <v>16817.900000000001</v>
       </c>
       <c r="AG13" s="5">
-        <f t="shared" si="18"/>
-        <v>17719.695</v>
+        <f t="shared" si="19"/>
+        <v>17983.3</v>
       </c>
       <c r="AH13" s="5">
-        <f t="shared" si="18"/>
-        <v>19086.555</v>
+        <f t="shared" si="19"/>
+        <v>19062.3</v>
       </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
@@ -2122,12 +2123,12 @@
       </c>
       <c r="AV13" s="5">
         <f>+AV12+AV11</f>
-        <v>53111.15</v>
+        <v>53795</v>
       </c>
     </row>
     <row r="14" spans="1:52" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="19" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -2197,32 +2198,29 @@
         <v>766</v>
       </c>
       <c r="AB14" s="20">
-        <f>+X14</f>
-        <v>1195</v>
+        <v>939</v>
       </c>
       <c r="AC14" s="20">
-        <f t="shared" ref="AC14:AC16" si="19">+Y14</f>
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="AD14" s="20">
-        <f t="shared" ref="AD14:AD16" si="20">+Z14</f>
-        <v>2007</v>
+        <v>1881</v>
       </c>
       <c r="AE14" s="20">
-        <f t="shared" ref="AE14:AE16" si="21">+AA14</f>
+        <f t="shared" ref="AE14:AE16" si="20">+AA14</f>
         <v>766</v>
       </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF16" si="22">+AB14</f>
-        <v>1195</v>
+        <f t="shared" ref="AF14:AF16" si="21">+AB14</f>
+        <v>939</v>
       </c>
       <c r="AG14" s="20">
-        <f t="shared" ref="AG14:AG16" si="23">+AC14</f>
-        <v>1129</v>
+        <f t="shared" ref="AG14:AG16" si="22">+AC14</f>
+        <v>1150</v>
       </c>
       <c r="AH14" s="20">
-        <f t="shared" ref="AH14:AH16" si="24">+AD14</f>
-        <v>2007</v>
+        <f t="shared" ref="AH14:AH16" si="23">+AD14</f>
+        <v>1881</v>
       </c>
       <c r="AI14" s="20"/>
       <c r="AJ14" s="20"/>
@@ -2247,25 +2245,25 @@
         <v>5878</v>
       </c>
       <c r="AS14" s="5">
-        <f t="shared" ref="AS14:AS16" si="25">SUM(O14:R14)</f>
+        <f t="shared" ref="AS14:AS16" si="24">SUM(O14:R14)</f>
         <v>5779</v>
       </c>
       <c r="AT14" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5081</v>
       </c>
       <c r="AU14" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5201</v>
       </c>
       <c r="AV14" s="5">
         <f t="shared" si="6"/>
-        <v>5097</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="15" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -2335,32 +2333,29 @@
         <v>670</v>
       </c>
       <c r="AB15" s="20">
-        <f t="shared" ref="AB15:AB16" si="26">+X15</f>
-        <v>728</v>
+        <v>776</v>
       </c>
       <c r="AC15" s="20">
-        <f t="shared" si="19"/>
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="AD15" s="20">
+        <v>924</v>
+      </c>
+      <c r="AE15" s="20">
         <f t="shared" si="20"/>
-        <v>850</v>
-      </c>
-      <c r="AE15" s="20">
+        <v>670</v>
+      </c>
+      <c r="AF15" s="20">
         <f t="shared" si="21"/>
-        <v>670</v>
-      </c>
-      <c r="AF15" s="20">
+        <v>776</v>
+      </c>
+      <c r="AG15" s="20">
         <f t="shared" si="22"/>
-        <v>728</v>
-      </c>
-      <c r="AG15" s="20">
+        <v>714</v>
+      </c>
+      <c r="AH15" s="20">
         <f t="shared" si="23"/>
-        <v>703</v>
-      </c>
-      <c r="AH15" s="20">
-        <f t="shared" si="24"/>
-        <v>850</v>
+        <v>924</v>
       </c>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
@@ -2385,25 +2380,25 @@
         <v>3183</v>
       </c>
       <c r="AS15" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>3274</v>
       </c>
       <c r="AT15" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3066</v>
       </c>
       <c r="AU15" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2936</v>
       </c>
       <c r="AV15" s="5">
         <f t="shared" si="6"/>
-        <v>2951</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="16" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -2473,32 +2468,29 @@
         <v>1349</v>
       </c>
       <c r="AB16" s="20">
-        <f t="shared" si="26"/>
-        <v>1330</v>
+        <v>1428</v>
       </c>
       <c r="AC16" s="20">
-        <f t="shared" si="19"/>
-        <v>1291</v>
+        <v>1443</v>
       </c>
       <c r="AD16" s="20">
+        <v>1523</v>
+      </c>
+      <c r="AE16" s="20">
         <f t="shared" si="20"/>
-        <v>1348</v>
-      </c>
-      <c r="AE16" s="20">
+        <v>1349</v>
+      </c>
+      <c r="AF16" s="20">
         <f t="shared" si="21"/>
-        <v>1349</v>
-      </c>
-      <c r="AF16" s="20">
+        <v>1428</v>
+      </c>
+      <c r="AG16" s="20">
         <f t="shared" si="22"/>
-        <v>1330</v>
-      </c>
-      <c r="AG16" s="20">
+        <v>1443</v>
+      </c>
+      <c r="AH16" s="20">
         <f t="shared" si="23"/>
-        <v>1291</v>
-      </c>
-      <c r="AH16" s="20">
-        <f t="shared" si="24"/>
-        <v>1348</v>
+        <v>1523</v>
       </c>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
@@ -2523,20 +2515,20 @@
         <v>3205</v>
       </c>
       <c r="AS16" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>5594</v>
       </c>
       <c r="AT16" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5431</v>
       </c>
       <c r="AU16" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5232</v>
       </c>
       <c r="AV16" s="5">
         <f t="shared" si="6"/>
-        <v>5318</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="18" spans="2:141" s="8" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -2548,83 +2540,83 @@
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9">
-        <f t="shared" ref="G18:Q18" si="27">SUM(G13:G16)</f>
+        <f t="shared" ref="G18:Q18" si="25">SUM(G13:G16)</f>
         <v>9367</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>9800</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>10085</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>11227</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>9728</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>10360</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>10513</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>11840</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>11445</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>12275</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="25"/>
         <v>12398</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" ref="R18:AH18" si="28">SUM(R13:R16)</f>
+        <f t="shared" ref="R18:AH18" si="26">SUM(R13:R16)</f>
         <v>13837</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>12453</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>12941</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>13280</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>14287</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="28"/>
+        <f>SUM(W13:W16)</f>
         <v>13307</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>14059</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>14130</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>15903</v>
       </c>
       <c r="AA18" s="9">
@@ -2632,51 +2624,51 @@
         <v>14926</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="28"/>
-        <v>15800.15</v>
+        <f t="shared" si="26"/>
+        <v>16058</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="28"/>
-        <v>16655.900000000001</v>
+        <f t="shared" si="26"/>
+        <v>17190</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="28"/>
-        <v>19095.099999999999</v>
+        <f t="shared" si="26"/>
+        <v>19184</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="28"/>
-        <v>18770.95</v>
+        <f t="shared" si="26"/>
+        <v>18557.95</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="28"/>
-        <v>19984.057500000003</v>
+        <f t="shared" si="26"/>
+        <v>19960.900000000001</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="28"/>
-        <v>20842.695</v>
+        <f t="shared" si="26"/>
+        <v>21290.3</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="28"/>
-        <v>23291.555</v>
+        <f t="shared" si="26"/>
+        <v>23390.3</v>
       </c>
       <c r="AI18" s="9"/>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9"/>
       <c r="AL18" s="9"/>
       <c r="AM18" s="9">
-        <f t="shared" ref="AM18:AP18" si="29">SUM(AM13:AM16)</f>
+        <f t="shared" ref="AM18:AP18" si="27">SUM(AM13:AM16)</f>
         <v>37728</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>39831</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>39506</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>39068</v>
       </c>
       <c r="AQ18" s="9">
@@ -2700,23 +2692,23 @@
         <v>57399</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" ref="AV18:AZ18" si="30">AU18*1.03</f>
+        <f t="shared" ref="AV18:AZ18" si="28">AU18*1.03</f>
         <v>59120.97</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>60894.599099999999</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>62721.437073000001</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>64603.080185190003</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>66541.1725907457</v>
       </c>
     </row>
@@ -2814,31 +2806,31 @@
       </c>
       <c r="AB19" s="5">
         <f>+AB18-AB20</f>
-        <v>5372.0509999999995</v>
+        <v>5459.7199999999993</v>
       </c>
       <c r="AC19" s="5">
-        <f t="shared" ref="AC19:AH19" si="31">+AC18-AC20</f>
-        <v>5829.5650000000005</v>
+        <f t="shared" ref="AC19:AH19" si="29">+AC18-AC20</f>
+        <v>6016.5</v>
       </c>
       <c r="AD19" s="5">
-        <f t="shared" si="31"/>
-        <v>6874.235999999999</v>
+        <f t="shared" si="29"/>
+        <v>6906.24</v>
       </c>
       <c r="AE19" s="5">
-        <f t="shared" si="31"/>
-        <v>6945.2515000000003</v>
+        <f t="shared" si="29"/>
+        <v>6866.4415000000008</v>
       </c>
       <c r="AF19" s="5">
-        <f t="shared" si="31"/>
-        <v>7593.9418500000011</v>
+        <f t="shared" si="29"/>
+        <v>7585.1419999999998</v>
       </c>
       <c r="AG19" s="5">
-        <f t="shared" si="31"/>
-        <v>8128.6510500000004</v>
+        <f t="shared" si="29"/>
+        <v>8303.2170000000006</v>
       </c>
       <c r="AH19" s="5">
-        <f t="shared" si="31"/>
-        <v>9316.6220000000012</v>
+        <f t="shared" si="29"/>
+        <v>9356.1200000000008</v>
       </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
@@ -2877,27 +2869,27 @@
         <v>10592.2</v>
       </c>
       <c r="AU19" s="3">
-        <f t="shared" ref="AU19:AZ19" si="32">AU18*0.2</f>
+        <f t="shared" ref="AU19:AZ19" si="30">AU18*0.2</f>
         <v>11479.800000000001</v>
       </c>
       <c r="AV19" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>11824.194000000001</v>
       </c>
       <c r="AW19" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>12178.919820000001</v>
       </c>
       <c r="AX19" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>12544.287414600001</v>
       </c>
       <c r="AY19" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>12920.616037038002</v>
       </c>
       <c r="AZ19" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>13308.23451814914</v>
       </c>
     </row>
@@ -2910,7 +2902,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5">
-        <f t="shared" ref="G20" si="33">G18-G19</f>
+        <f t="shared" ref="G20" si="31">G18-G19</f>
         <v>7487</v>
       </c>
       <c r="H20" s="5">
@@ -2926,27 +2918,27 @@
         <v>9105</v>
       </c>
       <c r="K20" s="5">
-        <f t="shared" ref="K20:O20" si="34">K18-K19</f>
+        <f t="shared" ref="K20:O20" si="32">K18-K19</f>
         <v>7625</v>
       </c>
       <c r="L20" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>8201</v>
       </c>
       <c r="M20" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>8295</v>
       </c>
       <c r="N20" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>9444</v>
       </c>
       <c r="O20" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>8408</v>
       </c>
       <c r="P20" s="5">
-        <f t="shared" ref="P20" si="35">P18*0.8</f>
+        <f t="shared" ref="P20" si="33">P18*0.8</f>
         <v>9820</v>
       </c>
       <c r="Q20" s="5">
@@ -2954,91 +2946,91 @@
         <v>8959</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" ref="R20:S20" si="36">+R18-R19</f>
+        <f t="shared" ref="R20:S20" si="34">+R18-R19</f>
         <v>10107</v>
       </c>
       <c r="S20" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>8843</v>
       </c>
       <c r="T20" s="5">
-        <f t="shared" ref="T20:AA20" si="37">+T18-T19</f>
+        <f t="shared" ref="T20:AA20" si="35">+T18-T19</f>
         <v>9201</v>
       </c>
       <c r="U20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>9411</v>
       </c>
       <c r="V20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>10364</v>
       </c>
       <c r="W20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>9401</v>
       </c>
       <c r="X20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>9974</v>
       </c>
       <c r="Y20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>9935</v>
       </c>
       <c r="Z20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>11163</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="35"/>
         <v>10042</v>
       </c>
       <c r="AB20" s="5">
         <f>+AB18*0.66</f>
-        <v>10428.099</v>
+        <v>10598.28</v>
       </c>
       <c r="AC20" s="5">
         <f>+AC18*0.65</f>
-        <v>10826.335000000001</v>
+        <v>11173.5</v>
       </c>
       <c r="AD20" s="5">
         <f>+AD18*0.64</f>
-        <v>12220.864</v>
+        <v>12277.76</v>
       </c>
       <c r="AE20" s="5">
         <f>+AE18*0.63</f>
-        <v>11825.6985</v>
+        <v>11691.5085</v>
       </c>
       <c r="AF20" s="5">
         <f>+AF18*0.62</f>
-        <v>12390.115650000002</v>
+        <v>12375.758000000002</v>
       </c>
       <c r="AG20" s="5">
         <f>+AG18*0.61</f>
-        <v>12714.043949999999</v>
+        <v>12987.082999999999</v>
       </c>
       <c r="AH20" s="5">
         <f>+AH18*0.6</f>
-        <v>13974.932999999999</v>
+        <v>14034.179999999998</v>
       </c>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
       <c r="AK20" s="5"/>
       <c r="AL20" s="5"/>
       <c r="AM20" s="5">
-        <f t="shared" ref="AM20:AO20" si="38">AM18-AM19</f>
+        <f t="shared" ref="AM20:AO20" si="36">AM18-AM19</f>
         <v>30259</v>
       </c>
       <c r="AN20" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>31750</v>
       </c>
       <c r="AO20" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>31511</v>
       </c>
       <c r="AP20" s="5">
-        <f t="shared" ref="AP20" si="39">AP18-AP19</f>
+        <f t="shared" ref="AP20" si="37">AP18-AP19</f>
         <v>31130</v>
       </c>
       <c r="AQ20" s="5">
@@ -3046,7 +3038,7 @@
         <v>32624</v>
       </c>
       <c r="AR20" s="5">
-        <f t="shared" ref="AR20" si="40">AR18-AR19</f>
+        <f t="shared" ref="AR20" si="38">AR18-AR19</f>
         <v>33563</v>
       </c>
       <c r="AS20" s="3">
@@ -3054,31 +3046,31 @@
         <v>36391</v>
       </c>
       <c r="AT20" s="3">
-        <f t="shared" ref="AT20:AZ20" si="41">AT18-AT19</f>
+        <f t="shared" ref="AT20:AZ20" si="39">AT18-AT19</f>
         <v>42368.800000000003</v>
       </c>
       <c r="AU20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>45919.199999999997</v>
       </c>
       <c r="AV20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>47296.775999999998</v>
       </c>
       <c r="AW20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>48715.679279999997</v>
       </c>
       <c r="AX20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>50177.149658399998</v>
       </c>
       <c r="AY20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>51682.464148152001</v>
       </c>
       <c r="AZ20" s="3">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>53232.93807259656</v>
       </c>
     </row>
@@ -3154,31 +3146,31 @@
         <v>2063</v>
       </c>
       <c r="AB21" s="5">
-        <f t="shared" ref="AB21" si="42">+X21*1.01</f>
+        <f t="shared" ref="AB21" si="40">+X21*1.01</f>
         <v>2211.9</v>
       </c>
       <c r="AC21" s="5">
-        <f t="shared" ref="AC21:AC23" si="43">+Y21*1.01</f>
+        <f t="shared" ref="AC21:AC23" si="41">+Y21*1.01</f>
         <v>2140.19</v>
       </c>
       <c r="AD21" s="5">
-        <f t="shared" ref="AD21:AD23" si="44">+Z21*1.01</f>
+        <f t="shared" ref="AD21:AD23" si="42">+Z21*1.01</f>
         <v>2329.06</v>
       </c>
       <c r="AE21" s="5">
-        <f t="shared" ref="AE21:AE23" si="45">+AA21*1.01</f>
+        <f t="shared" ref="AE21:AE23" si="43">+AA21*1.01</f>
         <v>2083.63</v>
       </c>
       <c r="AF21" s="5">
-        <f t="shared" ref="AF21:AF23" si="46">+AB21*1.01</f>
+        <f t="shared" ref="AF21:AF23" si="44">+AB21*1.01</f>
         <v>2234.0190000000002</v>
       </c>
       <c r="AG21" s="5">
-        <f t="shared" ref="AG21:AG23" si="47">+AC21*1.01</f>
+        <f t="shared" ref="AG21:AG23" si="45">+AC21*1.01</f>
         <v>2161.5918999999999</v>
       </c>
       <c r="AH21" s="5">
-        <f t="shared" ref="AH21:AH23" si="48">+AD21*1.01</f>
+        <f t="shared" ref="AH21:AH23" si="46">+AD21*1.01</f>
         <v>2352.3505999999998</v>
       </c>
       <c r="AI21" s="5"/>
@@ -3204,7 +3196,7 @@
         <v>8047</v>
       </c>
       <c r="AS21" s="3">
-        <f t="shared" ref="AS21:AS23" si="49">SUM(O21:R21)</f>
+        <f t="shared" ref="AS21:AS23" si="47">SUM(O21:R21)</f>
         <v>8832</v>
       </c>
       <c r="AT21" s="3">
@@ -3212,27 +3204,27 @@
         <v>9008.64</v>
       </c>
       <c r="AU21" s="3">
-        <f t="shared" ref="AU21:AZ21" si="50">AT21*1.02</f>
+        <f t="shared" ref="AU21:AZ21" si="48">AT21*1.02</f>
         <v>9188.8127999999997</v>
       </c>
       <c r="AV21" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>9372.5890560000007</v>
       </c>
       <c r="AW21" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>9560.040837120001</v>
       </c>
       <c r="AX21" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>9751.241653862402</v>
       </c>
       <c r="AY21" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>9946.2664869396503</v>
       </c>
       <c r="AZ21" s="3">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>10145.191816678444</v>
       </c>
     </row>
@@ -3312,27 +3304,27 @@
         <v>2495.71</v>
       </c>
       <c r="AC22" s="5">
+        <f t="shared" si="41"/>
+        <v>2453.29</v>
+      </c>
+      <c r="AD22" s="5">
+        <f t="shared" si="42"/>
+        <v>2680.54</v>
+      </c>
+      <c r="AE22" s="5">
         <f t="shared" si="43"/>
-        <v>2453.29</v>
-      </c>
-      <c r="AD22" s="5">
+        <v>2515.91</v>
+      </c>
+      <c r="AF22" s="5">
         <f t="shared" si="44"/>
-        <v>2680.54</v>
-      </c>
-      <c r="AE22" s="5">
+        <v>2520.6671000000001</v>
+      </c>
+      <c r="AG22" s="5">
         <f t="shared" si="45"/>
-        <v>2515.91</v>
-      </c>
-      <c r="AF22" s="5">
+        <v>2477.8229000000001</v>
+      </c>
+      <c r="AH22" s="5">
         <f t="shared" si="46"/>
-        <v>2520.6671000000001</v>
-      </c>
-      <c r="AG22" s="5">
-        <f t="shared" si="47"/>
-        <v>2477.8229000000001</v>
-      </c>
-      <c r="AH22" s="5">
-        <f t="shared" si="48"/>
         <v>2707.3454000000002</v>
       </c>
       <c r="AI22" s="5"/>
@@ -3358,35 +3350,35 @@
         <v>7219</v>
       </c>
       <c r="AS22" s="3">
+        <f t="shared" si="47"/>
+        <v>8686</v>
+      </c>
+      <c r="AT22" s="3">
+        <f t="shared" ref="AT22:AZ22" si="49">AS22*1.01</f>
+        <v>8772.86</v>
+      </c>
+      <c r="AU22" s="3">
         <f t="shared" si="49"/>
-        <v>8686</v>
-      </c>
-      <c r="AT22" s="3">
-        <f t="shared" ref="AT22:AZ22" si="51">AS22*1.01</f>
-        <v>8772.86</v>
-      </c>
-      <c r="AU22" s="3">
-        <f t="shared" si="51"/>
         <v>8860.588600000001</v>
       </c>
       <c r="AV22" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>8949.1944860000003</v>
       </c>
       <c r="AW22" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>9038.6864308599997</v>
       </c>
       <c r="AX22" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>9129.0732951686005</v>
       </c>
       <c r="AY22" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>9220.3640281202861</v>
       </c>
       <c r="AZ22" s="3">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>9312.5676684014888</v>
       </c>
     </row>
@@ -3462,31 +3454,31 @@
         <v>376</v>
       </c>
       <c r="AB23" s="5">
-        <f t="shared" ref="AB23" si="52">+X23*1.01</f>
+        <f t="shared" ref="AB23" si="50">+X23*1.01</f>
         <v>390.87</v>
       </c>
       <c r="AC23" s="5">
+        <f t="shared" si="41"/>
+        <v>393.9</v>
+      </c>
+      <c r="AD23" s="5">
+        <f t="shared" si="42"/>
+        <v>471.67</v>
+      </c>
+      <c r="AE23" s="5">
         <f t="shared" si="43"/>
-        <v>393.9</v>
-      </c>
-      <c r="AD23" s="5">
+        <v>379.76</v>
+      </c>
+      <c r="AF23" s="5">
         <f t="shared" si="44"/>
-        <v>471.67</v>
-      </c>
-      <c r="AE23" s="5">
+        <v>394.77870000000001</v>
+      </c>
+      <c r="AG23" s="5">
         <f t="shared" si="45"/>
-        <v>379.76</v>
-      </c>
-      <c r="AF23" s="5">
+        <v>397.839</v>
+      </c>
+      <c r="AH23" s="5">
         <f t="shared" si="46"/>
-        <v>394.77870000000001</v>
-      </c>
-      <c r="AG23" s="5">
-        <f t="shared" si="47"/>
-        <v>397.839</v>
-      </c>
-      <c r="AH23" s="5">
-        <f t="shared" si="48"/>
         <v>476.38670000000002</v>
       </c>
       <c r="AI23" s="5"/>
@@ -3512,35 +3504,35 @@
         <v>1317</v>
       </c>
       <c r="AS23" s="3">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>1579</v>
       </c>
       <c r="AT23" s="3">
-        <f t="shared" ref="AT23:AZ23" si="53">AS23*1.01</f>
+        <f t="shared" ref="AT23:AZ23" si="51">AS23*1.01</f>
         <v>1594.79</v>
       </c>
       <c r="AU23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1610.7379000000001</v>
       </c>
       <c r="AV23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1626.8452790000001</v>
       </c>
       <c r="AW23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1643.1137317900002</v>
       </c>
       <c r="AX23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1659.5448691079002</v>
       </c>
       <c r="AY23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1676.1403177989794</v>
       </c>
       <c r="AZ23" s="3">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>1692.9017209769693</v>
       </c>
     </row>
@@ -3549,47 +3541,47 @@
         <v>22</v>
       </c>
       <c r="C24" s="5">
-        <f t="shared" ref="C24:M24" si="54">SUM(C21:C23)</f>
+        <f t="shared" ref="C24:M24" si="52">SUM(C21:C23)</f>
         <v>0</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="E24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="F24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" ref="G24" si="55">SUM(G21:G23)</f>
+        <f t="shared" ref="G24" si="53">SUM(G21:G23)</f>
         <v>3738</v>
       </c>
       <c r="H24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>3761</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>3866</v>
       </c>
       <c r="J24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>4098</v>
       </c>
       <c r="K24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>3836</v>
       </c>
       <c r="L24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>4027</v>
       </c>
       <c r="M24" s="5">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>4155</v>
       </c>
       <c r="N24" s="5">
@@ -3597,83 +3589,83 @@
         <v>4567</v>
       </c>
       <c r="O24" s="5">
-        <f t="shared" ref="O24:T24" si="56">SUM(O21:O23)</f>
+        <f t="shared" ref="O24:T24" si="54">SUM(O21:O23)</f>
         <v>4681</v>
       </c>
       <c r="P24" s="5">
+        <f t="shared" si="54"/>
+        <v>4740</v>
+      </c>
+      <c r="Q24" s="5">
+        <f t="shared" si="54"/>
+        <v>4698</v>
+      </c>
+      <c r="R24" s="5">
+        <f t="shared" si="54"/>
+        <v>4978</v>
+      </c>
+      <c r="S24" s="5">
+        <f t="shared" si="54"/>
+        <v>4635</v>
+      </c>
+      <c r="T24" s="5">
+        <f t="shared" si="54"/>
+        <v>4694</v>
+      </c>
+      <c r="U24" s="5">
+        <f t="shared" ref="U24:AA24" si="55">SUM(U21:U23)</f>
+        <v>4667</v>
+      </c>
+      <c r="V24" s="5">
+        <f t="shared" si="55"/>
+        <v>4742</v>
+      </c>
+      <c r="W24" s="5">
+        <f t="shared" si="55"/>
+        <v>4700</v>
+      </c>
+      <c r="X24" s="5">
+        <f t="shared" si="55"/>
+        <v>5048</v>
+      </c>
+      <c r="Y24" s="5">
+        <f t="shared" si="55"/>
+        <v>4938</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="55"/>
+        <v>5427</v>
+      </c>
+      <c r="AA24" s="5">
+        <f t="shared" si="55"/>
+        <v>4930</v>
+      </c>
+      <c r="AB24" s="5">
+        <f t="shared" ref="AB24:AH24" si="56">SUM(AB21:AB23)</f>
+        <v>5098.4800000000005</v>
+      </c>
+      <c r="AC24" s="5">
         <f t="shared" si="56"/>
-        <v>4740</v>
-      </c>
-      <c r="Q24" s="5">
+        <v>4987.3799999999992</v>
+      </c>
+      <c r="AD24" s="5">
         <f t="shared" si="56"/>
-        <v>4698</v>
-      </c>
-      <c r="R24" s="5">
+        <v>5481.27</v>
+      </c>
+      <c r="AE24" s="5">
         <f t="shared" si="56"/>
-        <v>4978</v>
-      </c>
-      <c r="S24" s="5">
+        <v>4979.3</v>
+      </c>
+      <c r="AF24" s="5">
         <f t="shared" si="56"/>
-        <v>4635</v>
-      </c>
-      <c r="T24" s="5">
+        <v>5149.4648000000007</v>
+      </c>
+      <c r="AG24" s="5">
         <f t="shared" si="56"/>
-        <v>4694</v>
-      </c>
-      <c r="U24" s="5">
-        <f t="shared" ref="U24:AA24" si="57">SUM(U21:U23)</f>
-        <v>4667</v>
-      </c>
-      <c r="V24" s="5">
-        <f t="shared" si="57"/>
-        <v>4742</v>
-      </c>
-      <c r="W24" s="5">
-        <f t="shared" si="57"/>
-        <v>4700</v>
-      </c>
-      <c r="X24" s="5">
-        <f t="shared" si="57"/>
-        <v>5048</v>
-      </c>
-      <c r="Y24" s="5">
-        <f t="shared" si="57"/>
-        <v>4938</v>
-      </c>
-      <c r="Z24" s="5">
-        <f t="shared" si="57"/>
-        <v>5427</v>
-      </c>
-      <c r="AA24" s="5">
-        <f t="shared" si="57"/>
-        <v>4930</v>
-      </c>
-      <c r="AB24" s="5">
-        <f t="shared" ref="AB24:AH24" si="58">SUM(AB21:AB23)</f>
-        <v>5098.4800000000005</v>
-      </c>
-      <c r="AC24" s="5">
-        <f t="shared" si="58"/>
-        <v>4987.3799999999992</v>
-      </c>
-      <c r="AD24" s="5">
-        <f t="shared" si="58"/>
-        <v>5481.27</v>
-      </c>
-      <c r="AE24" s="5">
-        <f t="shared" si="58"/>
-        <v>4979.3</v>
-      </c>
-      <c r="AF24" s="5">
-        <f t="shared" si="58"/>
-        <v>5149.4648000000007</v>
-      </c>
-      <c r="AG24" s="5">
-        <f t="shared" si="58"/>
         <v>5037.2538000000004</v>
       </c>
       <c r="AH24" s="5">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>5536.0826999999999</v>
       </c>
       <c r="AI24" s="5"/>
@@ -3681,19 +3673,19 @@
       <c r="AK24" s="5"/>
       <c r="AL24" s="5"/>
       <c r="AM24" s="5">
-        <f t="shared" ref="AM24:AO24" si="59">SUM(AM21:AM23)</f>
+        <f t="shared" ref="AM24:AO24" si="57">SUM(AM21:AM23)</f>
         <v>15532</v>
       </c>
       <c r="AN24" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>15811</v>
       </c>
       <c r="AO24" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>15800</v>
       </c>
       <c r="AP24" s="5">
-        <f t="shared" ref="AP24" si="60">SUM(AP21:AP23)</f>
+        <f t="shared" ref="AP24" si="58">SUM(AP21:AP23)</f>
         <v>15342</v>
       </c>
       <c r="AQ24" s="5">
@@ -3705,35 +3697,35 @@
         <v>16583</v>
       </c>
       <c r="AS24" s="5">
-        <f t="shared" ref="AS24" si="61">SUM(AS21:AS23)</f>
+        <f t="shared" ref="AS24" si="59">SUM(AS21:AS23)</f>
         <v>19097</v>
       </c>
       <c r="AT24" s="5">
-        <f t="shared" ref="AT24" si="62">SUM(AT21:AT23)</f>
+        <f t="shared" ref="AT24" si="60">SUM(AT21:AT23)</f>
         <v>19376.29</v>
       </c>
       <c r="AU24" s="5">
-        <f t="shared" ref="AU24" si="63">SUM(AU21:AU23)</f>
+        <f t="shared" ref="AU24" si="61">SUM(AU21:AU23)</f>
         <v>19660.139300000003</v>
       </c>
       <c r="AV24" s="5">
-        <f t="shared" ref="AV24" si="64">SUM(AV21:AV23)</f>
+        <f t="shared" ref="AV24" si="62">SUM(AV21:AV23)</f>
         <v>19948.628821000002</v>
       </c>
       <c r="AW24" s="5">
-        <f t="shared" ref="AW24" si="65">SUM(AW21:AW23)</f>
+        <f t="shared" ref="AW24" si="63">SUM(AW21:AW23)</f>
         <v>20241.84099977</v>
       </c>
       <c r="AX24" s="5">
-        <f t="shared" ref="AX24" si="66">SUM(AX21:AX23)</f>
+        <f t="shared" ref="AX24" si="64">SUM(AX21:AX23)</f>
         <v>20539.859818138902</v>
       </c>
       <c r="AY24" s="5">
-        <f t="shared" ref="AY24" si="67">SUM(AY21:AY23)</f>
+        <f t="shared" ref="AY24" si="65">SUM(AY21:AY23)</f>
         <v>20842.770832858914</v>
       </c>
       <c r="AZ24" s="5">
-        <f t="shared" ref="AZ24" si="68">SUM(AZ21:AZ23)</f>
+        <f t="shared" ref="AZ24" si="66">SUM(AZ21:AZ23)</f>
         <v>21150.661206056902</v>
       </c>
     </row>
@@ -3742,47 +3734,47 @@
         <v>23</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:M25" si="69">C20-C24</f>
+        <f t="shared" ref="C25:M25" si="67">C20-C24</f>
         <v>0</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" ref="G25" si="70">G20-G24</f>
+        <f t="shared" ref="G25" si="68">G20-G24</f>
         <v>3749</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>4100</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>4304</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>5007</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>3789</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>4174</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>4140</v>
       </c>
       <c r="N25" s="5">
@@ -3790,103 +3782,103 @@
         <v>4877</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" ref="O25:T25" si="71">O20-O24</f>
+        <f t="shared" ref="O25:T25" si="69">O20-O24</f>
         <v>3727</v>
       </c>
       <c r="P25" s="5">
+        <f t="shared" si="69"/>
+        <v>5080</v>
+      </c>
+      <c r="Q25" s="5">
+        <f t="shared" si="69"/>
+        <v>4261</v>
+      </c>
+      <c r="R25" s="5">
+        <f t="shared" si="69"/>
+        <v>5129</v>
+      </c>
+      <c r="S25" s="5">
+        <f t="shared" si="69"/>
+        <v>4208</v>
+      </c>
+      <c r="T25" s="5">
+        <f t="shared" si="69"/>
+        <v>4507</v>
+      </c>
+      <c r="U25" s="5">
+        <f t="shared" ref="U25:AA25" si="70">U20-U24</f>
+        <v>4744</v>
+      </c>
+      <c r="V25" s="5">
+        <f t="shared" si="70"/>
+        <v>5622</v>
+      </c>
+      <c r="W25" s="5">
+        <f t="shared" si="70"/>
+        <v>4701</v>
+      </c>
+      <c r="X25" s="5">
+        <f t="shared" si="70"/>
+        <v>4926</v>
+      </c>
+      <c r="Y25" s="5">
+        <f t="shared" si="70"/>
+        <v>4997</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="70"/>
+        <v>5736</v>
+      </c>
+      <c r="AA25" s="5">
+        <f t="shared" si="70"/>
+        <v>5112</v>
+      </c>
+      <c r="AB25" s="5">
+        <f t="shared" ref="AB25:AH25" si="71">AB20-AB24</f>
+        <v>5499.8</v>
+      </c>
+      <c r="AC25" s="5">
         <f t="shared" si="71"/>
-        <v>5080</v>
-      </c>
-      <c r="Q25" s="5">
+        <v>6186.1200000000008</v>
+      </c>
+      <c r="AD25" s="5">
         <f t="shared" si="71"/>
-        <v>4261</v>
-      </c>
-      <c r="R25" s="5">
+        <v>6796.49</v>
+      </c>
+      <c r="AE25" s="5">
         <f t="shared" si="71"/>
-        <v>5129</v>
-      </c>
-      <c r="S25" s="5">
+        <v>6712.2084999999997</v>
+      </c>
+      <c r="AF25" s="5">
         <f t="shared" si="71"/>
-        <v>4208</v>
-      </c>
-      <c r="T25" s="5">
+        <v>7226.293200000001</v>
+      </c>
+      <c r="AG25" s="5">
         <f t="shared" si="71"/>
-        <v>4507</v>
-      </c>
-      <c r="U25" s="5">
-        <f t="shared" ref="U25:AA25" si="72">U20-U24</f>
-        <v>4744</v>
-      </c>
-      <c r="V25" s="5">
-        <f t="shared" si="72"/>
-        <v>5622</v>
-      </c>
-      <c r="W25" s="5">
-        <f t="shared" si="72"/>
-        <v>4701</v>
-      </c>
-      <c r="X25" s="5">
-        <f t="shared" si="72"/>
-        <v>4926</v>
-      </c>
-      <c r="Y25" s="5">
-        <f t="shared" si="72"/>
-        <v>4997</v>
-      </c>
-      <c r="Z25" s="5">
-        <f t="shared" si="72"/>
-        <v>5736</v>
-      </c>
-      <c r="AA25" s="5">
-        <f t="shared" si="72"/>
-        <v>5112</v>
-      </c>
-      <c r="AB25" s="5">
-        <f t="shared" ref="AB25:AH25" si="73">AB20-AB24</f>
-        <v>5329.6189999999997</v>
-      </c>
-      <c r="AC25" s="5">
-        <f t="shared" si="73"/>
-        <v>5838.9550000000017</v>
-      </c>
-      <c r="AD25" s="5">
-        <f t="shared" si="73"/>
-        <v>6739.5939999999991</v>
-      </c>
-      <c r="AE25" s="5">
-        <f t="shared" si="73"/>
-        <v>6846.3985000000002</v>
-      </c>
-      <c r="AF25" s="5">
-        <f t="shared" si="73"/>
-        <v>7240.6508500000009</v>
-      </c>
-      <c r="AG25" s="5">
-        <f t="shared" si="73"/>
-        <v>7676.7901499999989</v>
+        <v>7949.8291999999983</v>
       </c>
       <c r="AH25" s="5">
-        <f t="shared" si="73"/>
-        <v>8438.8502999999982</v>
+        <f t="shared" si="71"/>
+        <v>8498.0972999999976</v>
       </c>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
       <c r="AK25" s="5"/>
       <c r="AL25" s="5"/>
       <c r="AM25" s="5">
-        <f t="shared" ref="AM25:AO25" si="74">AM20-AM24</f>
+        <f t="shared" ref="AM25:AO25" si="72">AM20-AM24</f>
         <v>14727</v>
       </c>
       <c r="AN25" s="5">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>15939</v>
       </c>
       <c r="AO25" s="5">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>15711</v>
       </c>
       <c r="AP25" s="5">
-        <f t="shared" ref="AP25" si="75">AP20-AP24</f>
+        <f t="shared" ref="AP25" si="73">AP20-AP24</f>
         <v>15788</v>
       </c>
       <c r="AQ25" s="5">
@@ -3898,35 +3890,35 @@
         <v>16980</v>
       </c>
       <c r="AS25" s="5">
-        <f t="shared" ref="AS25" si="76">AS20-AS24</f>
+        <f t="shared" ref="AS25" si="74">AS20-AS24</f>
         <v>17294</v>
       </c>
       <c r="AT25" s="5">
-        <f t="shared" ref="AT25" si="77">AT20-AT24</f>
+        <f t="shared" ref="AT25" si="75">AT20-AT24</f>
         <v>22992.510000000002</v>
       </c>
       <c r="AU25" s="5">
-        <f t="shared" ref="AU25" si="78">AU20-AU24</f>
+        <f t="shared" ref="AU25" si="76">AU20-AU24</f>
         <v>26259.060699999995</v>
       </c>
       <c r="AV25" s="5">
-        <f t="shared" ref="AV25" si="79">AV20-AV24</f>
+        <f t="shared" ref="AV25" si="77">AV20-AV24</f>
         <v>27348.147178999996</v>
       </c>
       <c r="AW25" s="5">
-        <f t="shared" ref="AW25" si="80">AW20-AW24</f>
+        <f t="shared" ref="AW25" si="78">AW20-AW24</f>
         <v>28473.838280229997</v>
       </c>
       <c r="AX25" s="5">
-        <f t="shared" ref="AX25" si="81">AX20-AX24</f>
+        <f t="shared" ref="AX25" si="79">AX20-AX24</f>
         <v>29637.289840261095</v>
       </c>
       <c r="AY25" s="5">
-        <f t="shared" ref="AY25" si="82">AY20-AY24</f>
+        <f t="shared" ref="AY25" si="80">AY20-AY24</f>
         <v>30839.693315293087</v>
       </c>
       <c r="AZ25" s="5">
-        <f t="shared" ref="AZ25" si="83">AZ20-AZ24</f>
+        <f t="shared" ref="AZ25" si="81">AZ20-AZ24</f>
         <v>32082.276866539658</v>
       </c>
     </row>
@@ -4016,27 +4008,27 @@
         <v>-923</v>
       </c>
       <c r="AC26" s="5">
-        <f t="shared" ref="AC26:AH26" si="84">+AB26</f>
+        <f t="shared" ref="AC26:AH26" si="82">+AB26</f>
         <v>-923</v>
       </c>
       <c r="AD26" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-923</v>
       </c>
       <c r="AE26" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-923</v>
       </c>
       <c r="AF26" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-923</v>
       </c>
       <c r="AG26" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-923</v>
       </c>
       <c r="AH26" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>-923</v>
       </c>
       <c r="AI26" s="5"/>
@@ -4062,35 +4054,35 @@
         <v>-2755</v>
       </c>
       <c r="AS26" s="3">
-        <f t="shared" ref="AS26:AS28" si="85">SUM(O26:R26)</f>
+        <f t="shared" ref="AS26:AS28" si="83">SUM(O26:R26)</f>
         <v>-3833</v>
       </c>
       <c r="AT26" s="3">
-        <f t="shared" ref="AT26:AZ26" si="86">AS40*$BC$41</f>
+        <f t="shared" ref="AT26:AZ26" si="84">AS40*$BC$41</f>
         <v>0</v>
       </c>
       <c r="AU26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>195.43633500000004</v>
       </c>
       <c r="AV26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>420.29955979749997</v>
       </c>
       <c r="AW26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>656.33135707727865</v>
       </c>
       <c r="AX26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>903.9377989943905</v>
       </c>
       <c r="AY26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>1163.538233928062</v>
       </c>
       <c r="AZ26" s="3">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>1435.5657020964418</v>
       </c>
     </row>
@@ -4099,31 +4091,31 @@
         <v>25</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" ref="G27" si="87">+G25+G26</f>
+        <f t="shared" ref="G27" si="85">+G25+G26</f>
         <v>3135</v>
       </c>
       <c r="H27" s="5">
-        <f t="shared" ref="H27:J27" si="88">+H25+H26</f>
+        <f t="shared" ref="H27:J27" si="86">+H25+H26</f>
         <v>3500</v>
       </c>
       <c r="I27" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>3719</v>
       </c>
       <c r="J27" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>4310</v>
       </c>
       <c r="K27" s="5">
-        <f t="shared" ref="K27" si="89">+K25+K26</f>
+        <f t="shared" ref="K27" si="87">+K25+K26</f>
         <v>3084</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27" si="90">+L25+L26</f>
+        <f t="shared" ref="L27" si="88">+L25+L26</f>
         <v>3495</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" ref="M27" si="91">+M25+M26</f>
+        <f t="shared" ref="M27" si="89">+M25+M26</f>
         <v>3473</v>
       </c>
       <c r="N27" s="5">
@@ -4131,107 +4123,107 @@
         <v>4173</v>
       </c>
       <c r="O27" s="5">
-        <f t="shared" ref="O27:T27" si="92">+O25+O26</f>
+        <f t="shared" ref="O27:T27" si="90">+O25+O26</f>
         <v>2760</v>
       </c>
       <c r="P27" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>4153</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>3353</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>4098</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>3287</v>
       </c>
       <c r="T27" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>3605</v>
       </c>
       <c r="U27" s="5">
-        <f t="shared" ref="U27:AH27" si="93">+U25+U26</f>
+        <f t="shared" ref="U27:AH27" si="91">+U25+U26</f>
         <v>3859</v>
       </c>
       <c r="V27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>4720</v>
       </c>
       <c r="W27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>3879</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>4096</v>
       </c>
       <c r="Y27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>4087</v>
       </c>
       <c r="Z27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>4758</v>
       </c>
       <c r="AA27" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>4189</v>
       </c>
       <c r="AB27" s="5">
-        <f t="shared" si="93"/>
-        <v>4406.6189999999997</v>
+        <f t="shared" si="91"/>
+        <v>4576.8</v>
       </c>
       <c r="AC27" s="5">
-        <f t="shared" si="93"/>
-        <v>4915.9550000000017</v>
+        <f t="shared" si="91"/>
+        <v>5263.1200000000008</v>
       </c>
       <c r="AD27" s="5">
-        <f t="shared" si="93"/>
-        <v>5816.5939999999991</v>
+        <f t="shared" si="91"/>
+        <v>5873.49</v>
       </c>
       <c r="AE27" s="5">
-        <f t="shared" si="93"/>
-        <v>5923.3985000000002</v>
+        <f t="shared" si="91"/>
+        <v>5789.2084999999997</v>
       </c>
       <c r="AF27" s="5">
-        <f t="shared" si="93"/>
-        <v>6317.6508500000009</v>
+        <f t="shared" si="91"/>
+        <v>6303.293200000001</v>
       </c>
       <c r="AG27" s="5">
-        <f t="shared" si="93"/>
-        <v>6753.7901499999989</v>
+        <f t="shared" si="91"/>
+        <v>7026.8291999999983</v>
       </c>
       <c r="AH27" s="5">
-        <f t="shared" si="93"/>
-        <v>7515.8502999999982</v>
+        <f t="shared" si="91"/>
+        <v>7575.0972999999976</v>
       </c>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
       <c r="AK27" s="5"/>
       <c r="AL27" s="5"/>
       <c r="AM27" s="5">
-        <f t="shared" ref="AM27:AO27" si="94">+AM25+AM26</f>
+        <f t="shared" ref="AM27:AO27" si="92">+AM25+AM26</f>
         <v>12929</v>
       </c>
       <c r="AN27" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>13914</v>
       </c>
       <c r="AO27" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="92"/>
         <v>13629</v>
       </c>
       <c r="AP27" s="5">
-        <f t="shared" ref="AP27:AQ27" si="95">+AP25+AP26</f>
+        <f t="shared" ref="AP27:AQ27" si="93">+AP25+AP26</f>
         <v>13793</v>
       </c>
       <c r="AQ27" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>14665</v>
       </c>
       <c r="AR27" s="5">
@@ -4239,35 +4231,35 @@
         <v>14225</v>
       </c>
       <c r="AS27" s="5">
-        <f t="shared" ref="AS27" si="96">+AS25+AS26</f>
+        <f t="shared" ref="AS27" si="94">+AS25+AS26</f>
         <v>13461</v>
       </c>
       <c r="AT27" s="5">
-        <f t="shared" ref="AT27" si="97">+AT25+AT26</f>
+        <f t="shared" ref="AT27" si="95">+AT25+AT26</f>
         <v>22992.510000000002</v>
       </c>
       <c r="AU27" s="5">
-        <f t="shared" ref="AU27" si="98">+AU25+AU26</f>
+        <f t="shared" ref="AU27" si="96">+AU25+AU26</f>
         <v>26454.497034999993</v>
       </c>
       <c r="AV27" s="5">
-        <f t="shared" ref="AV27" si="99">+AV25+AV26</f>
+        <f t="shared" ref="AV27" si="97">+AV25+AV26</f>
         <v>27768.446738797495</v>
       </c>
       <c r="AW27" s="5">
-        <f t="shared" ref="AW27" si="100">+AW25+AW26</f>
+        <f t="shared" ref="AW27" si="98">+AW25+AW26</f>
         <v>29130.169637307274</v>
       </c>
       <c r="AX27" s="5">
-        <f t="shared" ref="AX27" si="101">+AX25+AX26</f>
+        <f t="shared" ref="AX27" si="99">+AX25+AX26</f>
         <v>30541.227639255485</v>
       </c>
       <c r="AY27" s="5">
-        <f t="shared" ref="AY27" si="102">+AY25+AY26</f>
+        <f t="shared" ref="AY27" si="100">+AY25+AY26</f>
         <v>32003.231549221149</v>
       </c>
       <c r="AZ27" s="5">
-        <f t="shared" ref="AZ27" si="103">+AZ25+AZ26</f>
+        <f t="shared" ref="AZ27" si="101">+AZ25+AZ26</f>
         <v>33517.842568636101</v>
       </c>
     </row>
@@ -4340,31 +4332,31 @@
       </c>
       <c r="AB28" s="5">
         <f>+AB27*0.15</f>
-        <v>660.99284999999998</v>
+        <v>686.52</v>
       </c>
       <c r="AC28" s="5">
-        <f t="shared" ref="AC28:AH28" si="104">+AC27*0.15</f>
-        <v>737.39325000000019</v>
+        <f t="shared" ref="AC28:AH28" si="102">+AC27*0.15</f>
+        <v>789.46800000000007</v>
       </c>
       <c r="AD28" s="5">
-        <f t="shared" si="104"/>
-        <v>872.48909999999989</v>
+        <f t="shared" si="102"/>
+        <v>881.0234999999999</v>
       </c>
       <c r="AE28" s="5">
-        <f t="shared" si="104"/>
-        <v>888.50977499999999</v>
+        <f t="shared" si="102"/>
+        <v>868.38127499999996</v>
       </c>
       <c r="AF28" s="5">
-        <f t="shared" si="104"/>
-        <v>947.64762750000011</v>
+        <f t="shared" si="102"/>
+        <v>945.49398000000008</v>
       </c>
       <c r="AG28" s="5">
-        <f t="shared" si="104"/>
-        <v>1013.0685224999997</v>
+        <f t="shared" si="102"/>
+        <v>1054.0243799999996</v>
       </c>
       <c r="AH28" s="5">
-        <f t="shared" si="104"/>
-        <v>1127.3775449999996</v>
+        <f t="shared" si="102"/>
+        <v>1136.2645949999996</v>
       </c>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
@@ -4388,7 +4380,7 @@
         <v>932</v>
       </c>
       <c r="AS28" s="3">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>623</v>
       </c>
       <c r="AT28" s="3">
@@ -4404,7 +4396,7 @@
         <v>4165.2670108196244</v>
       </c>
       <c r="AW28" s="3">
-        <f t="shared" ref="AW28:AZ28" si="105">AW27*0.15</f>
+        <f t="shared" ref="AW28:AZ28" si="103">AW27*0.15</f>
         <v>4369.5254455960912</v>
       </c>
       <c r="AX28" s="3">
@@ -4412,11 +4404,11 @@
         <v>4581.1841458883227</v>
       </c>
       <c r="AY28" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>4800.4847323831718</v>
       </c>
       <c r="AZ28" s="3">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>5027.6763852954145</v>
       </c>
     </row>
@@ -4425,7 +4417,7 @@
         <v>27</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" ref="G29" si="106">G27-G28</f>
+        <f t="shared" ref="G29" si="104">G27-G28</f>
         <v>2791</v>
       </c>
       <c r="H29" s="5">
@@ -4441,15 +4433,15 @@
         <v>4186</v>
       </c>
       <c r="K29" s="5">
-        <f t="shared" ref="K29:M29" si="107">K27-K28</f>
+        <f t="shared" ref="K29:M29" si="105">K27-K28</f>
         <v>2860</v>
       </c>
       <c r="L29" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>3495</v>
       </c>
       <c r="M29" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>2952</v>
       </c>
       <c r="N29" s="5">
@@ -4457,102 +4449,102 @@
         <v>3738</v>
       </c>
       <c r="O29" s="5">
-        <f t="shared" ref="O29:T29" si="108">O27-O28</f>
+        <f t="shared" ref="O29:T29" si="106">O27-O28</f>
         <v>2652</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>3750</v>
       </c>
       <c r="Q29" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>3031</v>
       </c>
       <c r="R29" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>4308</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>2509</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>2733</v>
       </c>
       <c r="U29" s="5">
-        <f t="shared" ref="U29:AH29" si="109">U27-U28</f>
+        <f t="shared" ref="U29:AH29" si="107">U27-U28</f>
         <v>2934</v>
       </c>
       <c r="V29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>3562</v>
       </c>
       <c r="W29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>2957</v>
       </c>
       <c r="X29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>3857</v>
       </c>
       <c r="Y29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>3575</v>
       </c>
       <c r="Z29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>4034</v>
       </c>
       <c r="AA29" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>3689</v>
       </c>
       <c r="AB29" s="5">
-        <f t="shared" si="109"/>
-        <v>3745.6261499999996</v>
+        <f t="shared" si="107"/>
+        <v>3890.28</v>
       </c>
       <c r="AC29" s="5">
-        <f t="shared" si="109"/>
-        <v>4178.5617500000017</v>
+        <f t="shared" si="107"/>
+        <v>4473.652000000001</v>
       </c>
       <c r="AD29" s="5">
-        <f t="shared" si="109"/>
-        <v>4944.1048999999994</v>
+        <f t="shared" si="107"/>
+        <v>4992.4664999999995</v>
       </c>
       <c r="AE29" s="5">
-        <f t="shared" si="109"/>
-        <v>5034.8887250000007</v>
+        <f t="shared" si="107"/>
+        <v>4920.827225</v>
       </c>
       <c r="AF29" s="5">
-        <f t="shared" si="109"/>
-        <v>5370.0032225000004</v>
+        <f t="shared" si="107"/>
+        <v>5357.7992200000008</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="109"/>
-        <v>5740.7216274999992</v>
+        <f t="shared" si="107"/>
+        <v>5972.8048199999985</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="109"/>
-        <v>6388.4727549999989</v>
+        <f t="shared" si="107"/>
+        <v>6438.832704999998</v>
       </c>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
       <c r="AM29" s="5">
-        <f t="shared" ref="AM29:AO29" si="110">AM27-AM28</f>
+        <f t="shared" ref="AM29:AO29" si="108">AM27-AM28</f>
         <v>10747</v>
       </c>
       <c r="AN29" s="5">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>4848</v>
       </c>
       <c r="AO29" s="5">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>12444</v>
       </c>
       <c r="AP29" s="5">
-        <f t="shared" ref="AP29" si="111">AP27-AP28</f>
+        <f t="shared" ref="AP29" si="109">AP27-AP28</f>
         <v>11865</v>
       </c>
       <c r="AQ29" s="5">
@@ -4564,391 +4556,391 @@
         <v>13293</v>
       </c>
       <c r="AS29" s="5">
-        <f t="shared" ref="AS29" si="112">AS27-AS28</f>
+        <f t="shared" ref="AS29" si="110">AS27-AS28</f>
         <v>12838</v>
       </c>
       <c r="AT29" s="5">
-        <f t="shared" ref="AT29" si="113">AT27-AT28</f>
+        <f t="shared" ref="AT29" si="111">AT27-AT28</f>
         <v>19543.633500000004</v>
       </c>
       <c r="AU29" s="5">
-        <f t="shared" ref="AU29" si="114">AU27-AU28</f>
+        <f t="shared" ref="AU29" si="112">AU27-AU28</f>
         <v>22486.322479749993</v>
       </c>
       <c r="AV29" s="5">
-        <f t="shared" ref="AV29" si="115">AV27-AV28</f>
+        <f t="shared" ref="AV29" si="113">AV27-AV28</f>
         <v>23603.179727977869</v>
       </c>
       <c r="AW29" s="5">
-        <f t="shared" ref="AW29" si="116">AW27-AW28</f>
+        <f t="shared" ref="AW29" si="114">AW27-AW28</f>
         <v>24760.644191711181</v>
       </c>
       <c r="AX29" s="5">
-        <f t="shared" ref="AX29" si="117">AX27-AX28</f>
+        <f t="shared" ref="AX29" si="115">AX27-AX28</f>
         <v>25960.043493367164</v>
       </c>
       <c r="AY29" s="5">
-        <f t="shared" ref="AY29" si="118">AY27-AY28</f>
+        <f t="shared" ref="AY29" si="116">AY27-AY28</f>
         <v>27202.746816837978</v>
       </c>
       <c r="AZ29" s="5">
-        <f t="shared" ref="AZ29" si="119">AZ27-AZ28</f>
+        <f t="shared" ref="AZ29" si="117">AZ27-AZ28</f>
         <v>28490.166183340687</v>
       </c>
       <c r="BA29" s="3">
-        <f t="shared" ref="BA29:CF29" si="120">AZ29*(1+$BC$40)</f>
+        <f t="shared" ref="BA29:CF29" si="118">AZ29*(1+$BC$40)</f>
         <v>28775.067845174093</v>
       </c>
       <c r="BB29" s="3">
+        <f t="shared" si="118"/>
+        <v>29062.818523625836</v>
+      </c>
+      <c r="BC29" s="3">
+        <f t="shared" si="118"/>
+        <v>29353.446708862095</v>
+      </c>
+      <c r="BD29" s="3">
+        <f t="shared" si="118"/>
+        <v>29646.981175950717</v>
+      </c>
+      <c r="BE29" s="3">
+        <f t="shared" si="118"/>
+        <v>29943.450987710225</v>
+      </c>
+      <c r="BF29" s="3">
+        <f t="shared" si="118"/>
+        <v>30242.885497587326</v>
+      </c>
+      <c r="BG29" s="3">
+        <f t="shared" si="118"/>
+        <v>30545.3143525632</v>
+      </c>
+      <c r="BH29" s="3">
+        <f t="shared" si="118"/>
+        <v>30850.767496088833</v>
+      </c>
+      <c r="BI29" s="3">
+        <f t="shared" si="118"/>
+        <v>31159.275171049721</v>
+      </c>
+      <c r="BJ29" s="3">
+        <f t="shared" si="118"/>
+        <v>31470.867922760219</v>
+      </c>
+      <c r="BK29" s="3">
+        <f t="shared" si="118"/>
+        <v>31785.576601987821</v>
+      </c>
+      <c r="BL29" s="3">
+        <f t="shared" si="118"/>
+        <v>32103.4323680077</v>
+      </c>
+      <c r="BM29" s="3">
+        <f t="shared" si="118"/>
+        <v>32424.466691687776</v>
+      </c>
+      <c r="BN29" s="3">
+        <f t="shared" si="118"/>
+        <v>32748.711358604654</v>
+      </c>
+      <c r="BO29" s="3">
+        <f t="shared" si="118"/>
+        <v>33076.198472190699</v>
+      </c>
+      <c r="BP29" s="3">
+        <f t="shared" si="118"/>
+        <v>33406.96045691261</v>
+      </c>
+      <c r="BQ29" s="3">
+        <f t="shared" si="118"/>
+        <v>33741.030061481739</v>
+      </c>
+      <c r="BR29" s="3">
+        <f t="shared" si="118"/>
+        <v>34078.440362096553</v>
+      </c>
+      <c r="BS29" s="3">
+        <f t="shared" si="118"/>
+        <v>34419.224765717518</v>
+      </c>
+      <c r="BT29" s="3">
+        <f t="shared" si="118"/>
+        <v>34763.417013374696</v>
+      </c>
+      <c r="BU29" s="3">
+        <f t="shared" si="118"/>
+        <v>35111.05118350844</v>
+      </c>
+      <c r="BV29" s="3">
+        <f t="shared" si="118"/>
+        <v>35462.161695343522</v>
+      </c>
+      <c r="BW29" s="3">
+        <f t="shared" si="118"/>
+        <v>35816.783312296961</v>
+      </c>
+      <c r="BX29" s="3">
+        <f t="shared" si="118"/>
+        <v>36174.951145419931</v>
+      </c>
+      <c r="BY29" s="3">
+        <f t="shared" si="118"/>
+        <v>36536.700656874127</v>
+      </c>
+      <c r="BZ29" s="3">
+        <f t="shared" si="118"/>
+        <v>36902.067663442867</v>
+      </c>
+      <c r="CA29" s="3">
+        <f t="shared" si="118"/>
+        <v>37271.088340077295</v>
+      </c>
+      <c r="CB29" s="3">
+        <f t="shared" si="118"/>
+        <v>37643.799223478069</v>
+      </c>
+      <c r="CC29" s="3">
+        <f t="shared" si="118"/>
+        <v>38020.237215712848</v>
+      </c>
+      <c r="CD29" s="3">
+        <f t="shared" si="118"/>
+        <v>38400.43958786998</v>
+      </c>
+      <c r="CE29" s="3">
+        <f t="shared" si="118"/>
+        <v>38784.443983748679</v>
+      </c>
+      <c r="CF29" s="3">
+        <f t="shared" si="118"/>
+        <v>39172.288423586164</v>
+      </c>
+      <c r="CG29" s="3">
+        <f t="shared" ref="CG29:DL29" si="119">CF29*(1+$BC$40)</f>
+        <v>39564.011307822024</v>
+      </c>
+      <c r="CH29" s="3">
+        <f t="shared" si="119"/>
+        <v>39959.651420900242</v>
+      </c>
+      <c r="CI29" s="3">
+        <f t="shared" si="119"/>
+        <v>40359.247935109248</v>
+      </c>
+      <c r="CJ29" s="3">
+        <f t="shared" si="119"/>
+        <v>40762.840414460341</v>
+      </c>
+      <c r="CK29" s="3">
+        <f t="shared" si="119"/>
+        <v>41170.468818604946</v>
+      </c>
+      <c r="CL29" s="3">
+        <f t="shared" si="119"/>
+        <v>41582.173506790998</v>
+      </c>
+      <c r="CM29" s="3">
+        <f t="shared" si="119"/>
+        <v>41997.995241858909</v>
+      </c>
+      <c r="CN29" s="3">
+        <f t="shared" si="119"/>
+        <v>42417.975194277496</v>
+      </c>
+      <c r="CO29" s="3">
+        <f t="shared" si="119"/>
+        <v>42842.154946220275</v>
+      </c>
+      <c r="CP29" s="3">
+        <f t="shared" si="119"/>
+        <v>43270.576495682479</v>
+      </c>
+      <c r="CQ29" s="3">
+        <f t="shared" si="119"/>
+        <v>43703.282260639302</v>
+      </c>
+      <c r="CR29" s="3">
+        <f t="shared" si="119"/>
+        <v>44140.315083245696</v>
+      </c>
+      <c r="CS29" s="3">
+        <f t="shared" si="119"/>
+        <v>44581.718234078151</v>
+      </c>
+      <c r="CT29" s="3">
+        <f t="shared" si="119"/>
+        <v>45027.535416418934</v>
+      </c>
+      <c r="CU29" s="3">
+        <f t="shared" si="119"/>
+        <v>45477.810770583121</v>
+      </c>
+      <c r="CV29" s="3">
+        <f t="shared" si="119"/>
+        <v>45932.588878288952</v>
+      </c>
+      <c r="CW29" s="3">
+        <f t="shared" si="119"/>
+        <v>46391.914767071845</v>
+      </c>
+      <c r="CX29" s="3">
+        <f t="shared" si="119"/>
+        <v>46855.833914742565</v>
+      </c>
+      <c r="CY29" s="3">
+        <f t="shared" si="119"/>
+        <v>47324.392253889993</v>
+      </c>
+      <c r="CZ29" s="3">
+        <f t="shared" si="119"/>
+        <v>47797.636176428896</v>
+      </c>
+      <c r="DA29" s="3">
+        <f t="shared" si="119"/>
+        <v>48275.612538193185</v>
+      </c>
+      <c r="DB29" s="3">
+        <f t="shared" si="119"/>
+        <v>48758.368663575115</v>
+      </c>
+      <c r="DC29" s="3">
+        <f t="shared" si="119"/>
+        <v>49245.952350210864</v>
+      </c>
+      <c r="DD29" s="3">
+        <f t="shared" si="119"/>
+        <v>49738.411873712976</v>
+      </c>
+      <c r="DE29" s="3">
+        <f t="shared" si="119"/>
+        <v>50235.795992450105</v>
+      </c>
+      <c r="DF29" s="3">
+        <f t="shared" si="119"/>
+        <v>50738.153952374603</v>
+      </c>
+      <c r="DG29" s="3">
+        <f t="shared" si="119"/>
+        <v>51245.53549189835</v>
+      </c>
+      <c r="DH29" s="3">
+        <f t="shared" si="119"/>
+        <v>51757.990846817331</v>
+      </c>
+      <c r="DI29" s="3">
+        <f t="shared" si="119"/>
+        <v>52275.570755285502</v>
+      </c>
+      <c r="DJ29" s="3">
+        <f t="shared" si="119"/>
+        <v>52798.326462838355</v>
+      </c>
+      <c r="DK29" s="3">
+        <f t="shared" si="119"/>
+        <v>53326.309727466738</v>
+      </c>
+      <c r="DL29" s="3">
+        <f t="shared" si="119"/>
+        <v>53859.572824741408</v>
+      </c>
+      <c r="DM29" s="3">
+        <f t="shared" ref="DM29:EK29" si="120">DL29*(1+$BC$40)</f>
+        <v>54398.16855298882</v>
+      </c>
+      <c r="DN29" s="3">
         <f t="shared" si="120"/>
-        <v>29062.818523625836</v>
-      </c>
-      <c r="BC29" s="3">
+        <v>54942.150238518712</v>
+      </c>
+      <c r="DO29" s="3">
         <f t="shared" si="120"/>
-        <v>29353.446708862095</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>55491.571740903899</v>
+      </c>
+      <c r="DP29" s="3">
         <f t="shared" si="120"/>
-        <v>29646.981175950717</v>
-      </c>
-      <c r="BE29" s="3">
+        <v>56046.487458312935</v>
+      </c>
+      <c r="DQ29" s="3">
         <f t="shared" si="120"/>
-        <v>29943.450987710225</v>
-      </c>
-      <c r="BF29" s="3">
+        <v>56606.952332896064</v>
+      </c>
+      <c r="DR29" s="3">
         <f t="shared" si="120"/>
-        <v>30242.885497587326</v>
-      </c>
-      <c r="BG29" s="3">
+        <v>57173.021856225023</v>
+      </c>
+      <c r="DS29" s="3">
         <f t="shared" si="120"/>
-        <v>30545.3143525632</v>
-      </c>
-      <c r="BH29" s="3">
+        <v>57744.752074787277</v>
+      </c>
+      <c r="DT29" s="3">
         <f t="shared" si="120"/>
-        <v>30850.767496088833</v>
-      </c>
-      <c r="BI29" s="3">
+        <v>58322.199595535152</v>
+      </c>
+      <c r="DU29" s="3">
         <f t="shared" si="120"/>
-        <v>31159.275171049721</v>
-      </c>
-      <c r="BJ29" s="3">
+        <v>58905.421591490507</v>
+      </c>
+      <c r="DV29" s="3">
         <f t="shared" si="120"/>
-        <v>31470.867922760219</v>
-      </c>
-      <c r="BK29" s="3">
+        <v>59494.475807405412</v>
+      </c>
+      <c r="DW29" s="3">
         <f t="shared" si="120"/>
-        <v>31785.576601987821</v>
-      </c>
-      <c r="BL29" s="3">
+        <v>60089.420565479464</v>
+      </c>
+      <c r="DX29" s="3">
         <f t="shared" si="120"/>
-        <v>32103.4323680077</v>
-      </c>
-      <c r="BM29" s="3">
+        <v>60690.314771134261</v>
+      </c>
+      <c r="DY29" s="3">
         <f t="shared" si="120"/>
-        <v>32424.466691687776</v>
-      </c>
-      <c r="BN29" s="3">
+        <v>61297.217918845607</v>
+      </c>
+      <c r="DZ29" s="3">
         <f t="shared" si="120"/>
-        <v>32748.711358604654</v>
-      </c>
-      <c r="BO29" s="3">
+        <v>61910.190098034065</v>
+      </c>
+      <c r="EA29" s="3">
         <f t="shared" si="120"/>
-        <v>33076.198472190699</v>
-      </c>
-      <c r="BP29" s="3">
+        <v>62529.291999014407</v>
+      </c>
+      <c r="EB29" s="3">
         <f t="shared" si="120"/>
-        <v>33406.96045691261</v>
-      </c>
-      <c r="BQ29" s="3">
+        <v>63154.584919004556</v>
+      </c>
+      <c r="EC29" s="3">
         <f t="shared" si="120"/>
-        <v>33741.030061481739</v>
-      </c>
-      <c r="BR29" s="3">
+        <v>63786.130768194598</v>
+      </c>
+      <c r="ED29" s="3">
         <f t="shared" si="120"/>
-        <v>34078.440362096553</v>
-      </c>
-      <c r="BS29" s="3">
+        <v>64423.992075876544</v>
+      </c>
+      <c r="EE29" s="3">
         <f t="shared" si="120"/>
-        <v>34419.224765717518</v>
-      </c>
-      <c r="BT29" s="3">
+        <v>65068.23199663531</v>
+      </c>
+      <c r="EF29" s="3">
         <f t="shared" si="120"/>
-        <v>34763.417013374696</v>
-      </c>
-      <c r="BU29" s="3">
+        <v>65718.914316601658</v>
+      </c>
+      <c r="EG29" s="3">
         <f t="shared" si="120"/>
-        <v>35111.05118350844</v>
-      </c>
-      <c r="BV29" s="3">
+        <v>66376.103459767677</v>
+      </c>
+      <c r="EH29" s="3">
         <f t="shared" si="120"/>
-        <v>35462.161695343522</v>
-      </c>
-      <c r="BW29" s="3">
+        <v>67039.864494365349</v>
+      </c>
+      <c r="EI29" s="3">
         <f t="shared" si="120"/>
-        <v>35816.783312296961</v>
-      </c>
-      <c r="BX29" s="3">
+        <v>67710.263139308998</v>
+      </c>
+      <c r="EJ29" s="3">
         <f t="shared" si="120"/>
-        <v>36174.951145419931</v>
-      </c>
-      <c r="BY29" s="3">
+        <v>68387.36577070209</v>
+      </c>
+      <c r="EK29" s="3">
         <f t="shared" si="120"/>
-        <v>36536.700656874127</v>
-      </c>
-      <c r="BZ29" s="3">
-        <f t="shared" si="120"/>
-        <v>36902.067663442867</v>
-      </c>
-      <c r="CA29" s="3">
-        <f t="shared" si="120"/>
-        <v>37271.088340077295</v>
-      </c>
-      <c r="CB29" s="3">
-        <f t="shared" si="120"/>
-        <v>37643.799223478069</v>
-      </c>
-      <c r="CC29" s="3">
-        <f t="shared" si="120"/>
-        <v>38020.237215712848</v>
-      </c>
-      <c r="CD29" s="3">
-        <f t="shared" si="120"/>
-        <v>38400.43958786998</v>
-      </c>
-      <c r="CE29" s="3">
-        <f t="shared" si="120"/>
-        <v>38784.443983748679</v>
-      </c>
-      <c r="CF29" s="3">
-        <f t="shared" si="120"/>
-        <v>39172.288423586164</v>
-      </c>
-      <c r="CG29" s="3">
-        <f t="shared" ref="CG29:DL29" si="121">CF29*(1+$BC$40)</f>
-        <v>39564.011307822024</v>
-      </c>
-      <c r="CH29" s="3">
-        <f t="shared" si="121"/>
-        <v>39959.651420900242</v>
-      </c>
-      <c r="CI29" s="3">
-        <f t="shared" si="121"/>
-        <v>40359.247935109248</v>
-      </c>
-      <c r="CJ29" s="3">
-        <f t="shared" si="121"/>
-        <v>40762.840414460341</v>
-      </c>
-      <c r="CK29" s="3">
-        <f t="shared" si="121"/>
-        <v>41170.468818604946</v>
-      </c>
-      <c r="CL29" s="3">
-        <f t="shared" si="121"/>
-        <v>41582.173506790998</v>
-      </c>
-      <c r="CM29" s="3">
-        <f t="shared" si="121"/>
-        <v>41997.995241858909</v>
-      </c>
-      <c r="CN29" s="3">
-        <f t="shared" si="121"/>
-        <v>42417.975194277496</v>
-      </c>
-      <c r="CO29" s="3">
-        <f t="shared" si="121"/>
-        <v>42842.154946220275</v>
-      </c>
-      <c r="CP29" s="3">
-        <f t="shared" si="121"/>
-        <v>43270.576495682479</v>
-      </c>
-      <c r="CQ29" s="3">
-        <f t="shared" si="121"/>
-        <v>43703.282260639302</v>
-      </c>
-      <c r="CR29" s="3">
-        <f t="shared" si="121"/>
-        <v>44140.315083245696</v>
-      </c>
-      <c r="CS29" s="3">
-        <f t="shared" si="121"/>
-        <v>44581.718234078151</v>
-      </c>
-      <c r="CT29" s="3">
-        <f t="shared" si="121"/>
-        <v>45027.535416418934</v>
-      </c>
-      <c r="CU29" s="3">
-        <f t="shared" si="121"/>
-        <v>45477.810770583121</v>
-      </c>
-      <c r="CV29" s="3">
-        <f t="shared" si="121"/>
-        <v>45932.588878288952</v>
-      </c>
-      <c r="CW29" s="3">
-        <f t="shared" si="121"/>
-        <v>46391.914767071845</v>
-      </c>
-      <c r="CX29" s="3">
-        <f t="shared" si="121"/>
-        <v>46855.833914742565</v>
-      </c>
-      <c r="CY29" s="3">
-        <f t="shared" si="121"/>
-        <v>47324.392253889993</v>
-      </c>
-      <c r="CZ29" s="3">
-        <f t="shared" si="121"/>
-        <v>47797.636176428896</v>
-      </c>
-      <c r="DA29" s="3">
-        <f t="shared" si="121"/>
-        <v>48275.612538193185</v>
-      </c>
-      <c r="DB29" s="3">
-        <f t="shared" si="121"/>
-        <v>48758.368663575115</v>
-      </c>
-      <c r="DC29" s="3">
-        <f t="shared" si="121"/>
-        <v>49245.952350210864</v>
-      </c>
-      <c r="DD29" s="3">
-        <f t="shared" si="121"/>
-        <v>49738.411873712976</v>
-      </c>
-      <c r="DE29" s="3">
-        <f t="shared" si="121"/>
-        <v>50235.795992450105</v>
-      </c>
-      <c r="DF29" s="3">
-        <f t="shared" si="121"/>
-        <v>50738.153952374603</v>
-      </c>
-      <c r="DG29" s="3">
-        <f t="shared" si="121"/>
-        <v>51245.53549189835</v>
-      </c>
-      <c r="DH29" s="3">
-        <f t="shared" si="121"/>
-        <v>51757.990846817331</v>
-      </c>
-      <c r="DI29" s="3">
-        <f t="shared" si="121"/>
-        <v>52275.570755285502</v>
-      </c>
-      <c r="DJ29" s="3">
-        <f t="shared" si="121"/>
-        <v>52798.326462838355</v>
-      </c>
-      <c r="DK29" s="3">
-        <f t="shared" si="121"/>
-        <v>53326.309727466738</v>
-      </c>
-      <c r="DL29" s="3">
-        <f t="shared" si="121"/>
-        <v>53859.572824741408</v>
-      </c>
-      <c r="DM29" s="3">
-        <f t="shared" ref="DM29:EK29" si="122">DL29*(1+$BC$40)</f>
-        <v>54398.16855298882</v>
-      </c>
-      <c r="DN29" s="3">
-        <f t="shared" si="122"/>
-        <v>54942.150238518712</v>
-      </c>
-      <c r="DO29" s="3">
-        <f t="shared" si="122"/>
-        <v>55491.571740903899</v>
-      </c>
-      <c r="DP29" s="3">
-        <f t="shared" si="122"/>
-        <v>56046.487458312935</v>
-      </c>
-      <c r="DQ29" s="3">
-        <f t="shared" si="122"/>
-        <v>56606.952332896064</v>
-      </c>
-      <c r="DR29" s="3">
-        <f t="shared" si="122"/>
-        <v>57173.021856225023</v>
-      </c>
-      <c r="DS29" s="3">
-        <f t="shared" si="122"/>
-        <v>57744.752074787277</v>
-      </c>
-      <c r="DT29" s="3">
-        <f t="shared" si="122"/>
-        <v>58322.199595535152</v>
-      </c>
-      <c r="DU29" s="3">
-        <f t="shared" si="122"/>
-        <v>58905.421591490507</v>
-      </c>
-      <c r="DV29" s="3">
-        <f t="shared" si="122"/>
-        <v>59494.475807405412</v>
-      </c>
-      <c r="DW29" s="3">
-        <f t="shared" si="122"/>
-        <v>60089.420565479464</v>
-      </c>
-      <c r="DX29" s="3">
-        <f t="shared" si="122"/>
-        <v>60690.314771134261</v>
-      </c>
-      <c r="DY29" s="3">
-        <f t="shared" si="122"/>
-        <v>61297.217918845607</v>
-      </c>
-      <c r="DZ29" s="3">
-        <f t="shared" si="122"/>
-        <v>61910.190098034065</v>
-      </c>
-      <c r="EA29" s="3">
-        <f t="shared" si="122"/>
-        <v>62529.291999014407</v>
-      </c>
-      <c r="EB29" s="3">
-        <f t="shared" si="122"/>
-        <v>63154.584919004556</v>
-      </c>
-      <c r="EC29" s="3">
-        <f t="shared" si="122"/>
-        <v>63786.130768194598</v>
-      </c>
-      <c r="ED29" s="3">
-        <f t="shared" si="122"/>
-        <v>64423.992075876544</v>
-      </c>
-      <c r="EE29" s="3">
-        <f t="shared" si="122"/>
-        <v>65068.23199663531</v>
-      </c>
-      <c r="EF29" s="3">
-        <f t="shared" si="122"/>
-        <v>65718.914316601658</v>
-      </c>
-      <c r="EG29" s="3">
-        <f t="shared" si="122"/>
-        <v>66376.103459767677</v>
-      </c>
-      <c r="EH29" s="3">
-        <f t="shared" si="122"/>
-        <v>67039.864494365349</v>
-      </c>
-      <c r="EI29" s="3">
-        <f t="shared" si="122"/>
-        <v>67710.263139308998</v>
-      </c>
-      <c r="EJ29" s="3">
-        <f t="shared" si="122"/>
-        <v>68387.36577070209</v>
-      </c>
-      <c r="EK29" s="3">
-        <f t="shared" si="122"/>
         <v>69071.239428409113</v>
       </c>
     </row>
@@ -4957,7 +4949,7 @@
         <v>28</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" ref="G30" si="123">G29/G31</f>
+        <f t="shared" ref="G30" si="121">G29/G31</f>
         <v>0.89829417444480208</v>
       </c>
       <c r="H30" s="6">
@@ -4973,118 +4965,118 @@
         <v>1.4223581379544683</v>
       </c>
       <c r="K30" s="6">
-        <f t="shared" ref="K30:T30" si="124">K29/K31</f>
+        <f t="shared" ref="K30:T30" si="122">K29/K31</f>
         <v>0.99965047186298495</v>
       </c>
       <c r="L30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.2973273942093542</v>
       </c>
       <c r="M30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.0718954248366013</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.363238512035011</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>0.96541681834728799</v>
       </c>
       <c r="P30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.3656227239621268</v>
       </c>
       <c r="Q30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.0918587896253602</v>
       </c>
       <c r="R30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>1.5407725321888412</v>
       </c>
       <c r="S30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>0.88877081119376555</v>
       </c>
       <c r="T30" s="6">
-        <f t="shared" si="124"/>
+        <f t="shared" si="122"/>
         <v>0.9701810436634718</v>
       </c>
       <c r="U30" s="6">
-        <f t="shared" ref="U30:AH30" si="125">U29/U31</f>
+        <f t="shared" ref="U30:AH30" si="123">U29/U31</f>
         <v>1.0407946080170274</v>
       </c>
       <c r="V30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.2568807339449541</v>
       </c>
       <c r="W30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.0371799368642582</v>
       </c>
       <c r="X30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.3443708609271523</v>
       </c>
       <c r="Y30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.2439109255393179</v>
       </c>
       <c r="Z30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.4050853361198188</v>
       </c>
       <c r="AA30" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="123"/>
         <v>1.2681333791680991</v>
       </c>
       <c r="AB30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.2875992265383291</v>
+        <f t="shared" si="123"/>
+        <v>1.3373255414231695</v>
       </c>
       <c r="AC30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.4364254898590587</v>
+        <f t="shared" si="123"/>
+        <v>1.5378659333104163</v>
       </c>
       <c r="AD30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.6995891715366103</v>
+        <f t="shared" si="123"/>
+        <v>1.7162139910622205</v>
       </c>
       <c r="AE30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.7307970866277074</v>
+        <f t="shared" si="123"/>
+        <v>1.6915872206943967</v>
       </c>
       <c r="AF30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.8459962951185975</v>
+        <f t="shared" si="123"/>
+        <v>1.8418010381574428</v>
       </c>
       <c r="AG30" s="6">
-        <f t="shared" si="125"/>
-        <v>1.9734347292884149</v>
+        <f t="shared" si="123"/>
+        <v>2.0532158198693704</v>
       </c>
       <c r="AH30" s="6">
-        <f t="shared" si="125"/>
-        <v>2.1961061378480573</v>
+        <f t="shared" si="123"/>
+        <v>2.2134179116534884</v>
       </c>
       <c r="AI30" s="6"/>
       <c r="AJ30" s="6"/>
       <c r="AK30" s="6"/>
       <c r="AM30" s="6">
-        <f t="shared" ref="AM30:AO30" si="126">AM29/AM31</f>
+        <f t="shared" ref="AM30:AO30" si="124">AM29/AM31</f>
         <v>2.5484941901825944</v>
       </c>
       <c r="AN30" s="6">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>1.1439358187824447</v>
       </c>
       <c r="AO30" s="6">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.334405144694534</v>
       </c>
       <c r="AP30" s="6">
-        <f t="shared" ref="AP30" si="127">AP29/AP31</f>
+        <f t="shared" ref="AP30" si="125">AP29/AP31</f>
         <v>3.6020036429872495</v>
       </c>
       <c r="AQ30" s="6">
@@ -5092,39 +5084,39 @@
         <v>4.852746525479815</v>
       </c>
       <c r="AR30" s="6">
-        <f t="shared" ref="AR30:AS30" si="128">AR29/AR31</f>
+        <f t="shared" ref="AR30:AS30" si="126">AR29/AR31</f>
         <v>4.7713567839195976</v>
       </c>
       <c r="AS30" s="6">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>4.6409399005874379</v>
       </c>
       <c r="AT30" s="6">
-        <f t="shared" ref="AT30:AZ30" si="129">AT29/AT31</f>
+        <f t="shared" ref="AT30:AZ30" si="127">AT29/AT31</f>
         <v>7.0650279258924549</v>
       </c>
       <c r="AU30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>8.1288106569362828</v>
       </c>
       <c r="AV30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>8.5325548045107524</v>
       </c>
       <c r="AW30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>8.9509784696651362</v>
       </c>
       <c r="AX30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>9.3845615882032227</v>
       </c>
       <c r="AY30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>9.8337991204113795</v>
       </c>
       <c r="AZ30" s="6">
-        <f t="shared" si="129"/>
+        <f t="shared" si="127"/>
         <v>10.299201512278604</v>
       </c>
     </row>
@@ -5204,27 +5196,27 @@
         <v>2909</v>
       </c>
       <c r="AC31" s="5">
-        <f t="shared" ref="AC31:AH31" si="130">+AB31</f>
+        <f t="shared" ref="AC31:AH31" si="128">+AB31</f>
         <v>2909</v>
       </c>
       <c r="AD31" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>2909</v>
       </c>
       <c r="AE31" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>2909</v>
       </c>
       <c r="AF31" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>2909</v>
       </c>
       <c r="AG31" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>2909</v>
       </c>
       <c r="AH31" s="5">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>2909</v>
       </c>
       <c r="AI31" s="5"/>
@@ -5258,27 +5250,27 @@
         <v>2766.25</v>
       </c>
       <c r="AU31" s="3">
-        <f t="shared" ref="AU31:AZ31" si="131">AT31</f>
+        <f t="shared" ref="AU31:AZ31" si="129">AT31</f>
         <v>2766.25</v>
       </c>
       <c r="AV31" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2766.25</v>
       </c>
       <c r="AW31" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2766.25</v>
       </c>
       <c r="AX31" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2766.25</v>
       </c>
       <c r="AY31" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2766.25</v>
       </c>
       <c r="AZ31" s="3">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2766.25</v>
       </c>
     </row>
@@ -5320,43 +5312,43 @@
         <v>5.4600516611739591E-2</v>
       </c>
       <c r="O34" s="7">
-        <f t="shared" ref="O34:R34" si="132">O18/K18-1</f>
+        <f t="shared" ref="O34:R34" si="130">O18/K18-1</f>
         <v>0.17650082236842102</v>
       </c>
       <c r="P34" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.18484555984555984</v>
       </c>
       <c r="Q34" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.17930181679824986</v>
       </c>
       <c r="R34" s="7">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.16866554054054061</v>
       </c>
       <c r="S34" s="7">
-        <f t="shared" ref="S34" si="133">S18/O18-1</f>
+        <f t="shared" ref="S34" si="131">S18/O18-1</f>
         <v>8.8073394495412849E-2</v>
       </c>
       <c r="T34" s="7">
-        <f t="shared" ref="T34" si="134">T18/P18-1</f>
+        <f t="shared" ref="T34" si="132">T18/P18-1</f>
         <v>5.425661914460278E-2</v>
       </c>
       <c r="U34" s="7">
-        <f t="shared" ref="U34" si="135">U18/Q18-1</f>
+        <f t="shared" ref="U34" si="133">U18/Q18-1</f>
         <v>7.114050653331172E-2</v>
       </c>
       <c r="V34" s="7">
-        <f t="shared" ref="V34:AB34" si="136">V18/R18-1</f>
+        <f t="shared" ref="V34:AB34" si="134">V18/R18-1</f>
         <v>3.2521500325215058E-2</v>
       </c>
       <c r="W34" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>6.857785272625061E-2</v>
       </c>
       <c r="X34" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>8.6392087164824938E-2</v>
       </c>
       <c r="Y34" s="7">
@@ -5364,40 +5356,40 @@
         <v>6.4006024096385561E-2</v>
       </c>
       <c r="Z34" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.11310982011618953</v>
       </c>
       <c r="AA34" s="7">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.12166528894566775</v>
       </c>
       <c r="AB34" s="7">
-        <f t="shared" si="136"/>
-        <v>0.12384593498826368</v>
+        <f t="shared" si="134"/>
+        <v>0.14218649975104913</v>
       </c>
       <c r="AC34" s="7">
-        <f t="shared" ref="AC34" si="137">AC18/Y18-1</f>
-        <v>0.17876150035385718</v>
+        <f t="shared" ref="AC34" si="135">AC18/Y18-1</f>
+        <v>0.21656050955414008</v>
       </c>
       <c r="AD34" s="7">
-        <f t="shared" ref="AD34" si="138">AD18/Z18-1</f>
-        <v>0.20072313399987407</v>
+        <f t="shared" ref="AD34" si="136">AD18/Z18-1</f>
+        <v>0.20631327422498891</v>
       </c>
       <c r="AE34" s="7">
-        <f t="shared" ref="AE34" si="139">AE18/AA18-1</f>
-        <v>0.25760083076510787</v>
+        <f t="shared" ref="AE34" si="137">AE18/AA18-1</f>
+        <v>0.243330430121935</v>
       </c>
       <c r="AF34" s="7">
-        <f t="shared" ref="AF34" si="140">AF18/AB18-1</f>
-        <v>0.26480175821115637</v>
+        <f t="shared" ref="AF34" si="138">AF18/AB18-1</f>
+        <v>0.24305019305019315</v>
       </c>
       <c r="AG34" s="7">
-        <f t="shared" ref="AG34" si="141">AG18/AC18-1</f>
-        <v>0.25137008507495828</v>
+        <f t="shared" ref="AG34" si="139">AG18/AC18-1</f>
+        <v>0.23852821407795233</v>
       </c>
       <c r="AH34" s="7">
-        <f t="shared" ref="AH34" si="142">AH18/AD18-1</f>
-        <v>0.21976606563987633</v>
+        <f t="shared" ref="AH34" si="140">AH18/AD18-1</f>
+        <v>0.21926084236864041</v>
       </c>
       <c r="AI34" s="7"/>
       <c r="AJ34" s="7"/>
@@ -5406,11 +5398,11 @@
       <c r="AM34" s="7"/>
       <c r="AO34" s="13"/>
       <c r="AP34" s="13">
-        <f t="shared" ref="AP34:AQ34" si="143">AP18/AO18-1</f>
+        <f t="shared" ref="AP34:AQ34" si="141">AP18/AO18-1</f>
         <v>-1.108692350529028E-2</v>
       </c>
       <c r="AQ34" s="13">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>3.6116514794716892E-2</v>
       </c>
       <c r="AR34" s="13">
@@ -5418,15 +5410,15 @@
         <v>4.8444872650015958E-2</v>
       </c>
       <c r="AS34" s="13">
-        <f t="shared" ref="AS34:AZ34" si="144">AS18/AR18-1</f>
+        <f t="shared" ref="AS34:AZ34" si="142">AS18/AR18-1</f>
         <v>0.17707351555136674</v>
       </c>
       <c r="AT34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>6.0174156741066964E-2</v>
       </c>
       <c r="AU34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>8.3797511376295875E-2</v>
       </c>
       <c r="AV34" s="13">
@@ -5434,25 +5426,25 @@
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AW34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AX34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ34" s="13">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="35" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -5513,31 +5505,31 @@
         <v>18</v>
       </c>
       <c r="G36" s="7">
-        <f t="shared" ref="G36:M36" si="145">G20/G18</f>
+        <f t="shared" ref="G36:M36" si="143">G20/G18</f>
         <v>0.79929539874025834</v>
       </c>
       <c r="H36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.80214285714285716</v>
       </c>
       <c r="I36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.8101140307387209</v>
       </c>
       <c r="J36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.81099136011401085</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.78381990131578949</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.79160231660231661</v>
       </c>
       <c r="M36" s="7">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>0.78902311423951299</v>
       </c>
       <c r="N36" s="7">
@@ -5545,83 +5537,83 @@
         <v>0.79763513513513518</v>
       </c>
       <c r="O36" s="7">
-        <f t="shared" ref="O36:AA36" si="146">O20/O18</f>
+        <f t="shared" ref="O36:AA36" si="144">O20/O18</f>
         <v>0.73464394932284838</v>
       </c>
       <c r="P36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.8</v>
       </c>
       <c r="Q36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.72261655105662204</v>
       </c>
       <c r="R36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.73043289730432892</v>
       </c>
       <c r="S36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.71011001365132898</v>
       </c>
       <c r="T36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.71099605903716867</v>
       </c>
       <c r="U36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.70865963855421688</v>
       </c>
       <c r="V36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.72541471267585922</v>
       </c>
       <c r="W36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.70647027880063129</v>
       </c>
       <c r="X36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.70943879365530982</v>
       </c>
       <c r="Y36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.70311394196744514</v>
       </c>
       <c r="Z36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.70194302961705335</v>
       </c>
       <c r="AA36" s="7">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>0.67278574299879401</v>
       </c>
       <c r="AB36" s="7">
-        <f t="shared" ref="AB36:AH36" si="147">AB20/AB18</f>
+        <f t="shared" ref="AB36:AH36" si="145">AB20/AB18</f>
         <v>0.66</v>
       </c>
       <c r="AC36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.65</v>
       </c>
       <c r="AD36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.64</v>
       </c>
       <c r="AE36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.63</v>
       </c>
       <c r="AF36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.62</v>
       </c>
       <c r="AG36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.61</v>
       </c>
       <c r="AH36" s="7">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>0.6</v>
       </c>
       <c r="AI36" s="7"/>
@@ -5631,15 +5623,15 @@
       <c r="AM36" s="7"/>
       <c r="AN36" s="7"/>
       <c r="AO36" s="7">
-        <f t="shared" ref="AO36:AQ36" si="148">AO20/AO18</f>
+        <f t="shared" ref="AO36:AQ36" si="146">AO20/AO18</f>
         <v>0.79762567711233734</v>
       </c>
       <c r="AP36" s="7">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>0.79681580833418653</v>
       </c>
       <c r="AQ36" s="7">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>0.80594876355641198</v>
       </c>
       <c r="AR36" s="7">
@@ -5647,120 +5639,120 @@
         <v>0.79083411875589071</v>
       </c>
       <c r="AS36" s="7">
-        <f t="shared" ref="AS36:AZ36" si="149">AS20/AS18</f>
+        <f t="shared" ref="AS36:AZ36" si="147">AS20/AS18</f>
         <v>0.72847562806525878</v>
       </c>
       <c r="AT36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.8</v>
       </c>
       <c r="AU36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="AV36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="AW36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="AX36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="AY36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="AZ36" s="7">
-        <f t="shared" si="149"/>
+        <f t="shared" si="147"/>
         <v>0.8</v>
       </c>
     </row>
     <row r="37" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G37" s="7">
-        <f t="shared" ref="G37:Z37" si="150">+G25/G18</f>
+        <f t="shared" ref="G37:Z37" si="148">+G25/G18</f>
         <v>0.40023486708658057</v>
       </c>
       <c r="H37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.41836734693877553</v>
       </c>
       <c r="I37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.4267724343083788</v>
       </c>
       <c r="J37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.44597844482052196</v>
       </c>
       <c r="K37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.38949424342105265</v>
       </c>
       <c r="L37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.40289575289575291</v>
       </c>
       <c r="M37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.39379815466565204</v>
       </c>
       <c r="N37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.41190878378378376</v>
       </c>
       <c r="O37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.32564438619484493</v>
       </c>
       <c r="P37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.41384928716904279</v>
       </c>
       <c r="Q37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.34368446523632845</v>
       </c>
       <c r="R37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.37067283370672832</v>
       </c>
       <c r="S37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.33791054364410184</v>
       </c>
       <c r="T37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.34827293099451356</v>
       </c>
       <c r="U37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.35722891566265058</v>
       </c>
       <c r="V37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.39350458458738713</v>
       </c>
       <c r="W37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.35327271360937851</v>
       </c>
       <c r="X37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.35038053915641226</v>
       </c>
       <c r="Y37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.35364472753007786</v>
       </c>
       <c r="Z37" s="7">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.36068666289379364</v>
       </c>
       <c r="AA37" s="7">
@@ -5768,32 +5760,32 @@
         <v>0.3424896154361517</v>
       </c>
       <c r="AB37" s="7">
-        <f t="shared" ref="AB37:AH37" si="151">+AB25/AB18</f>
-        <v>0.33731445587541892</v>
+        <f t="shared" ref="AB37:AH37" si="149">+AB25/AB18</f>
+        <v>0.34249595217337153</v>
       </c>
       <c r="AC37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.3505637641916679</v>
+        <f t="shared" si="149"/>
+        <v>0.35986736474694597</v>
       </c>
       <c r="AD37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.35294887170006961</v>
+        <f t="shared" si="149"/>
+        <v>0.35427908673894909</v>
       </c>
       <c r="AE37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.36473372418551003</v>
+        <f t="shared" si="149"/>
+        <v>0.36168911436877454</v>
       </c>
       <c r="AF37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.36232135791242592</v>
+        <f t="shared" si="149"/>
+        <v>0.36202241381901618</v>
       </c>
       <c r="AG37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.36832041873663646</v>
+        <f t="shared" si="149"/>
+        <v>0.37340146451670475</v>
       </c>
       <c r="AH37" s="7">
-        <f t="shared" si="151"/>
-        <v>0.36231373560073588</v>
+        <f t="shared" si="149"/>
+        <v>0.36331715711213614</v>
       </c>
       <c r="AI37" s="7"/>
       <c r="AJ37" s="7"/>
@@ -5802,15 +5794,15 @@
       <c r="AM37" s="7"/>
       <c r="AN37" s="7"/>
       <c r="AO37" s="7">
-        <f t="shared" ref="AO37:AQ37" si="152">AO25/AO18</f>
+        <f t="shared" ref="AO37:AQ37" si="150">AO25/AO18</f>
         <v>0.39768642737811977</v>
       </c>
       <c r="AP37" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="150"/>
         <v>0.40411590048121226</v>
       </c>
       <c r="AQ37" s="7">
-        <f t="shared" si="152"/>
+        <f t="shared" si="150"/>
         <v>0.42394822006472493</v>
       </c>
       <c r="AR37" s="7">
@@ -5818,72 +5810,72 @@
         <v>0.40009425070688032</v>
       </c>
       <c r="AS37" s="7">
-        <f t="shared" ref="AS37:AZ37" si="153">AS25/AS18</f>
+        <f t="shared" ref="AS37:AZ37" si="151">AS25/AS18</f>
         <v>0.34619157241517368</v>
       </c>
       <c r="AT37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.43414040520382929</v>
       </c>
       <c r="AU37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.45748289517238966</v>
       </c>
       <c r="AV37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.46257947356073481</v>
       </c>
       <c r="AW37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.46759217896271521</v>
       </c>
       <c r="AX37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.47252249347805841</v>
       </c>
       <c r="AY37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.47737187185020574</v>
       </c>
       <c r="AZ37" s="7">
-        <f t="shared" si="153"/>
+        <f t="shared" si="151"/>
         <v>0.48214174198369242</v>
       </c>
     </row>
     <row r="38" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G38" s="7">
-        <f t="shared" ref="G38:J38" si="154">G28/G27</f>
+        <f t="shared" ref="G38:J38" si="152">G28/G27</f>
         <v>0.10972886762360447</v>
       </c>
       <c r="H38" s="7">
-        <f t="shared" si="154"/>
+        <f t="shared" si="152"/>
         <v>0.15142857142857144</v>
       </c>
       <c r="I38" s="7">
-        <f t="shared" si="154"/>
+        <f t="shared" si="152"/>
         <v>0</v>
       </c>
       <c r="J38" s="7">
-        <f t="shared" si="154"/>
+        <f t="shared" si="152"/>
         <v>2.877030162412993E-2</v>
       </c>
       <c r="K38" s="7">
-        <f t="shared" ref="K38:N38" si="155">K28/K27</f>
+        <f t="shared" ref="K38:N38" si="153">K28/K27</f>
         <v>7.2632944228274973E-2</v>
       </c>
       <c r="L38" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>0</v>
       </c>
       <c r="M38" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>0.15001439677512238</v>
       </c>
       <c r="N38" s="7">
-        <f t="shared" si="155"/>
+        <f t="shared" si="153"/>
         <v>0.10424155283968368</v>
       </c>
       <c r="O38" s="7">
@@ -5891,79 +5883,79 @@
         <v>3.9130434782608699E-2</v>
       </c>
       <c r="P38" s="7">
-        <f t="shared" ref="P38:AA38" si="156">P28/P27</f>
+        <f t="shared" ref="P38:AA38" si="154">P28/P27</f>
         <v>9.7038285576691544E-2</v>
       </c>
       <c r="Q38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>9.6033402922755737E-2</v>
       </c>
       <c r="R38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>-5.1244509516837483E-2</v>
       </c>
       <c r="S38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.23668999087313661</v>
       </c>
       <c r="T38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.2418862690707351</v>
       </c>
       <c r="U38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.23969940399067116</v>
       </c>
       <c r="V38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.24533898305084745</v>
       </c>
       <c r="W38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.2376901263212168</v>
       </c>
       <c r="X38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>5.8349609375E-2</v>
       </c>
       <c r="Y38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.12527526302911671</v>
       </c>
       <c r="Z38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.15216477511559479</v>
       </c>
       <c r="AA38" s="7">
-        <f t="shared" si="156"/>
+        <f t="shared" si="154"/>
         <v>0.11936022917164001</v>
       </c>
       <c r="AB38" s="7">
-        <f t="shared" ref="AB38:AH38" si="157">AB28/AB27</f>
+        <f t="shared" ref="AB38:AH38" si="155">AB28/AB27</f>
         <v>0.15</v>
       </c>
       <c r="AC38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AD38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AE38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AF38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AG38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AH38" s="7">
-        <f t="shared" si="157"/>
+        <f t="shared" si="155"/>
         <v>0.15</v>
       </c>
       <c r="AI38" s="7"/>
@@ -5973,117 +5965,126 @@
       <c r="AM38" s="7"/>
       <c r="AN38" s="7"/>
       <c r="AO38" s="7">
-        <f t="shared" ref="AO38:AZ38" si="158">AO28/AO27</f>
+        <f t="shared" ref="AO38:AZ38" si="156">AO28/AO27</f>
         <v>8.6946951353731011E-2</v>
       </c>
       <c r="AP38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.13978104835786268</v>
       </c>
       <c r="AQ38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0</v>
       </c>
       <c r="AR38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>6.5518453427065027E-2</v>
       </c>
       <c r="AS38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>4.6281851274050961E-2</v>
       </c>
       <c r="AT38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AU38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AV38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AW38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AX38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AY38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
       <c r="AZ38" s="7">
-        <f t="shared" si="158"/>
+        <f t="shared" si="156"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="40" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N40" s="5">
-        <f t="shared" ref="N40:U40" si="159">N41-N50</f>
+        <f t="shared" ref="N40:U40" si="157">N41-N51</f>
         <v>-53957</v>
       </c>
       <c r="O40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="P40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-83569</v>
       </c>
       <c r="Q40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-83042</v>
       </c>
       <c r="R40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>0</v>
       </c>
       <c r="S40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-76858</v>
       </c>
       <c r="T40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-80099</v>
       </c>
       <c r="U40" s="5">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-78076</v>
       </c>
       <c r="V40" s="5">
-        <f t="shared" ref="V40:AA40" si="160">+V41-V50</f>
+        <f t="shared" ref="V40:AD40" si="158">+V41-V51</f>
         <v>-76208</v>
       </c>
       <c r="W40" s="5">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>-73604</v>
       </c>
       <c r="X40" s="5">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>-77313</v>
       </c>
       <c r="Y40" s="5">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>-78453</v>
       </c>
       <c r="Z40" s="5">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>-81365</v>
       </c>
       <c r="AA40" s="5">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
         <v>-80310</v>
       </c>
-      <c r="AB40" s="5"/>
-      <c r="AC40" s="5"/>
-      <c r="AD40" s="5"/>
+      <c r="AB40" s="5">
+        <f t="shared" si="158"/>
+        <v>0</v>
+      </c>
+      <c r="AC40" s="5">
+        <f t="shared" si="158"/>
+        <v>-95473</v>
+      </c>
+      <c r="AD40" s="5">
+        <f t="shared" si="158"/>
+        <v>-97647</v>
+      </c>
       <c r="AE40" s="5"/>
       <c r="AF40" s="5"/>
       <c r="AG40" s="5"/>
@@ -6100,31 +6101,31 @@
         <v>19543.633500000004</v>
       </c>
       <c r="AU40" s="3">
-        <f t="shared" ref="AU40:AZ40" si="161">AT40+AU29</f>
+        <f t="shared" ref="AU40:AZ40" si="159">AT40+AU29</f>
         <v>42029.955979749997</v>
       </c>
       <c r="AV40" s="3">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>65633.135707727866</v>
       </c>
       <c r="AW40" s="3">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>90393.779899439047</v>
       </c>
       <c r="AX40" s="3">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>116353.82339280621</v>
       </c>
       <c r="AY40" s="3">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>143556.57020964418</v>
       </c>
       <c r="AZ40" s="3">
-        <f t="shared" si="161"/>
+        <f t="shared" si="159"/>
         <v>172046.73639298487</v>
       </c>
       <c r="BB40" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BC40" s="14">
         <v>0.01</v>
@@ -6196,8 +6197,14 @@
         <v>11005</v>
       </c>
       <c r="AB41" s="5"/>
-      <c r="AC41" s="5"/>
-      <c r="AD41" s="5"/>
+      <c r="AC41" s="5">
+        <f>38455+677</f>
+        <v>39132</v>
+      </c>
+      <c r="AD41" s="5">
+        <f>31289+605</f>
+        <v>31894</v>
+      </c>
       <c r="AE41" s="5"/>
       <c r="AF41" s="5"/>
       <c r="AG41" s="5"/>
@@ -6212,7 +6219,7 @@
       <c r="AQ41" s="5"/>
       <c r="AR41" s="5"/>
       <c r="BB41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="BC41" s="14">
         <v>0.01</v>
@@ -6220,7 +6227,7 @@
     </row>
     <row r="42" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -6272,8 +6279,12 @@
         <v>8843</v>
       </c>
       <c r="AB42" s="5"/>
-      <c r="AC42" s="5"/>
-      <c r="AD42" s="5"/>
+      <c r="AC42" s="5">
+        <v>10719</v>
+      </c>
+      <c r="AD42" s="5">
+        <v>10385</v>
+      </c>
       <c r="AE42" s="5"/>
       <c r="AF42" s="5"/>
       <c r="AG42" s="5"/>
@@ -6288,7 +6299,7 @@
       <c r="AQ42" s="5"/>
       <c r="AR42" s="5"/>
       <c r="BB42" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="BC42" s="14">
         <v>0.06</v>
@@ -6296,7 +6307,7 @@
     </row>
     <row r="43" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -6348,8 +6359,12 @@
         <v>4786</v>
       </c>
       <c r="AB43" s="5"/>
-      <c r="AC43" s="5"/>
-      <c r="AD43" s="5"/>
+      <c r="AC43" s="5">
+        <v>5023</v>
+      </c>
+      <c r="AD43" s="5">
+        <v>4288</v>
+      </c>
       <c r="AE43" s="5"/>
       <c r="AF43" s="5"/>
       <c r="AG43" s="5"/>
@@ -6364,7 +6379,7 @@
       <c r="AQ43" s="5"/>
       <c r="AR43" s="5"/>
       <c r="BB43" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="BC43" s="3">
         <f>NPV(BC42,AT29:EK29)+N40</f>
@@ -6373,7 +6388,7 @@
     </row>
     <row r="44" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -6425,8 +6440,12 @@
         <v>53194</v>
       </c>
       <c r="AB44" s="5"/>
-      <c r="AC44" s="5"/>
-      <c r="AD44" s="5"/>
+      <c r="AC44" s="5">
+        <v>83617</v>
+      </c>
+      <c r="AD44" s="5">
+        <v>99957</v>
+      </c>
       <c r="AE44" s="5"/>
       <c r="AF44" s="5"/>
       <c r="AG44" s="5"/>
@@ -6441,7 +6460,7 @@
       <c r="AQ44" s="5"/>
       <c r="AR44" s="5"/>
       <c r="BB44" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BC44" s="15">
         <f>BC43/O31</f>
@@ -6450,7 +6469,7 @@
     </row>
     <row r="45" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -6463,59 +6482,25 @@
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
-      <c r="N45" s="5">
-        <f>1440+43811</f>
-        <v>45251</v>
-      </c>
+      <c r="N45" s="5"/>
       <c r="O45" s="5"/>
-      <c r="P45" s="5">
-        <f>11593+61513</f>
-        <v>73106</v>
-      </c>
-      <c r="Q45" s="5">
-        <f>10707+61499</f>
-        <v>72206</v>
-      </c>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
-      <c r="S45" s="5">
-        <f>9074+62206</f>
-        <v>71280</v>
-      </c>
-      <c r="T45" s="5">
-        <f>8378+62231</f>
-        <v>70609</v>
-      </c>
-      <c r="U45" s="5">
-        <f>7629+62222</f>
-        <v>69851</v>
-      </c>
-      <c r="V45" s="5">
-        <f>6890+62230</f>
-        <v>69120</v>
-      </c>
-      <c r="W45" s="5">
-        <f>62249+6270</f>
-        <v>68519</v>
-      </c>
-      <c r="X45" s="5">
-        <f>5679+62204</f>
-        <v>67883</v>
-      </c>
-      <c r="Y45" s="5">
-        <f>5131+62171</f>
-        <v>67302</v>
-      </c>
-      <c r="Z45" s="5">
-        <f>4587+62207</f>
-        <v>66794</v>
-      </c>
-      <c r="AA45" s="5">
-        <f>4167+62211</f>
-        <v>66378</v>
-      </c>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
       <c r="AB45" s="5"/>
       <c r="AC45" s="5"/>
-      <c r="AD45" s="5"/>
+      <c r="AD45" s="5">
+        <v>29690</v>
+      </c>
       <c r="AE45" s="5"/>
       <c r="AF45" s="5"/>
       <c r="AG45" s="5"/>
@@ -6529,17 +6514,12 @@
       <c r="AP45" s="5"/>
       <c r="AQ45" s="5"/>
       <c r="AR45" s="5"/>
-      <c r="BB45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="BC45" s="14">
-        <f>BC44/Main!G2-1</f>
-        <v>-0.36225120625768292</v>
-      </c>
+      <c r="BB45" s="1"/>
+      <c r="BC45" s="15"/>
     </row>
     <row r="46" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -6553,46 +6533,63 @@
       <c r="L46" s="5"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
-        <v>12782</v>
+        <f>1440+43811</f>
+        <v>45251</v>
       </c>
       <c r="O46" s="5"/>
       <c r="P46" s="5">
-        <v>12091</v>
+        <f>11593+61513</f>
+        <v>73106</v>
       </c>
       <c r="Q46" s="5">
-        <v>12153</v>
+        <f>10707+61499</f>
+        <v>72206</v>
       </c>
       <c r="R46" s="5"/>
       <c r="S46" s="5">
-        <v>12243</v>
+        <f>9074+62206</f>
+        <v>71280</v>
       </c>
       <c r="T46" s="5">
-        <v>12758</v>
+        <f>8378+62231</f>
+        <v>70609</v>
       </c>
       <c r="U46" s="5">
-        <v>12688</v>
+        <f>7629+62222</f>
+        <v>69851</v>
       </c>
       <c r="V46" s="5">
-        <v>12273</v>
+        <f>6890+62230</f>
+        <v>69120</v>
       </c>
       <c r="W46" s="5">
-        <v>12219</v>
+        <f>62249+6270</f>
+        <v>68519</v>
       </c>
       <c r="X46" s="5">
-        <v>11984</v>
+        <f>5679+62204</f>
+        <v>67883</v>
       </c>
       <c r="Y46" s="5">
-        <v>11799</v>
+        <f>5131+62171</f>
+        <v>67302</v>
       </c>
       <c r="Z46" s="5">
-        <v>11877</v>
+        <f>4587+62207</f>
+        <v>66794</v>
       </c>
       <c r="AA46" s="5">
-        <v>11734</v>
+        <f>4167+62211</f>
+        <v>66378</v>
       </c>
       <c r="AB46" s="5"/>
-      <c r="AC46" s="5"/>
-      <c r="AD46" s="5"/>
+      <c r="AC46" s="5">
+        <f>3641+62274</f>
+        <v>65915</v>
+      </c>
+      <c r="AD46" s="5">
+        <v>62261</v>
+      </c>
       <c r="AE46" s="5"/>
       <c r="AF46" s="5"/>
       <c r="AG46" s="5"/>
@@ -6606,10 +6603,17 @@
       <c r="AP46" s="5"/>
       <c r="AQ46" s="5"/>
       <c r="AR46" s="5"/>
+      <c r="BB46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC46" s="14">
+        <f>BC44/Main!G2-1</f>
+        <v>0.11393455973658062</v>
+      </c>
     </row>
     <row r="47" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -6623,46 +6627,50 @@
       <c r="L47" s="5"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
-        <v>9915</v>
+        <v>12782</v>
       </c>
       <c r="O47" s="5"/>
       <c r="P47" s="5">
-        <v>11360</v>
+        <v>12091</v>
       </c>
       <c r="Q47" s="5">
-        <v>12220</v>
+        <v>12153</v>
       </c>
       <c r="R47" s="5"/>
       <c r="S47" s="5">
-        <v>13329</v>
+        <v>12243</v>
       </c>
       <c r="T47" s="5">
-        <v>13659</v>
+        <v>12758</v>
       </c>
       <c r="U47" s="5">
-        <v>14363</v>
+        <v>12688</v>
       </c>
       <c r="V47" s="5">
-        <v>15493</v>
+        <v>12273</v>
       </c>
       <c r="W47" s="5">
-        <v>17310</v>
+        <v>12219</v>
       </c>
       <c r="X47" s="5">
-        <v>18681</v>
+        <v>11984</v>
       </c>
       <c r="Y47" s="5">
-        <v>20191</v>
+        <v>11799</v>
       </c>
       <c r="Z47" s="5">
-        <v>21589</v>
+        <v>11877</v>
       </c>
       <c r="AA47" s="5">
-        <v>24509</v>
+        <v>11734</v>
       </c>
       <c r="AB47" s="5"/>
-      <c r="AC47" s="5"/>
-      <c r="AD47" s="5"/>
+      <c r="AC47" s="5">
+        <v>11360</v>
+      </c>
+      <c r="AD47" s="5">
+        <v>11541</v>
+      </c>
       <c r="AE47" s="5"/>
       <c r="AF47" s="5"/>
       <c r="AG47" s="5"/>
@@ -6679,7 +6687,7 @@
     </row>
     <row r="48" spans="2:55" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -6693,64 +6701,50 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
-        <f t="shared" ref="N48:AA48" si="162">SUM(N41:N47)</f>
-        <v>109297</v>
-      </c>
-      <c r="O48" s="5">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
+        <v>9915</v>
+      </c>
+      <c r="O48" s="5"/>
       <c r="P48" s="5">
-        <f t="shared" si="162"/>
-        <v>128469</v>
+        <v>11360</v>
       </c>
       <c r="Q48" s="5">
-        <f t="shared" si="162"/>
-        <v>131620</v>
-      </c>
-      <c r="R48" s="5">
-        <f t="shared" si="162"/>
-        <v>0</v>
-      </c>
+        <v>12220</v>
+      </c>
+      <c r="R48" s="5"/>
       <c r="S48" s="5">
-        <f t="shared" si="162"/>
-        <v>136662</v>
+        <v>13329</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" si="162"/>
-        <v>134324</v>
+        <v>13659</v>
       </c>
       <c r="U48" s="5">
-        <f t="shared" si="162"/>
-        <v>137082</v>
+        <v>14363</v>
       </c>
       <c r="V48" s="5">
-        <f t="shared" si="162"/>
-        <v>140976</v>
+        <v>15493</v>
       </c>
       <c r="W48" s="5">
-        <f t="shared" si="162"/>
-        <v>144214</v>
+        <v>17310</v>
       </c>
       <c r="X48" s="5">
-        <f t="shared" si="162"/>
-        <v>148483</v>
+        <v>18681</v>
       </c>
       <c r="Y48" s="5">
-        <f t="shared" si="162"/>
-        <v>161378</v>
+        <v>20191</v>
       </c>
       <c r="Z48" s="5">
-        <f t="shared" si="162"/>
-        <v>168361</v>
+        <v>21589</v>
       </c>
       <c r="AA48" s="5">
-        <f t="shared" si="162"/>
-        <v>180449</v>
+        <v>24509</v>
       </c>
       <c r="AB48" s="5"/>
-      <c r="AC48" s="5"/>
-      <c r="AD48" s="5"/>
+      <c r="AC48" s="5">
+        <v>29474</v>
+      </c>
+      <c r="AD48" s="5">
+        <v>11743</v>
+      </c>
       <c r="AE48" s="5"/>
       <c r="AF48" s="5"/>
       <c r="AG48" s="5"/>
@@ -6765,91 +6759,106 @@
       <c r="AQ48" s="5"/>
       <c r="AR48" s="5"/>
     </row>
-    <row r="50" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5">
-        <f>3749+72110</f>
-        <v>75859</v>
-      </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5">
-        <f>81173+9746</f>
-        <v>90919</v>
-      </c>
-      <c r="Q50" s="5">
-        <f>5415+86396</f>
-        <v>91811</v>
-      </c>
-      <c r="R50" s="5"/>
-      <c r="S50" s="5">
-        <f>84442+4499</f>
-        <v>88941</v>
-      </c>
-      <c r="T50" s="5">
-        <f>82468+6321</f>
-        <v>88789</v>
-      </c>
-      <c r="U50" s="5">
-        <f>5510+82470</f>
-        <v>87980</v>
-      </c>
-      <c r="V50" s="5">
-        <f>10605+76264</f>
-        <v>86869</v>
-      </c>
-      <c r="W50" s="5">
-        <f>9201+75314</f>
-        <v>84515</v>
-      </c>
-      <c r="X50" s="5">
-        <f>8162+80462</f>
-        <v>88624</v>
-      </c>
-      <c r="Y50" s="5">
-        <f>8167+88109</f>
-        <v>96276</v>
-      </c>
-      <c r="Z50" s="5">
-        <f>7271+85297</f>
-        <v>92568</v>
-      </c>
-      <c r="AA50" s="5">
-        <f>9079+82236</f>
-        <v>91315</v>
-      </c>
-      <c r="AB50" s="5"/>
-      <c r="AC50" s="5"/>
-      <c r="AD50" s="5"/>
-      <c r="AE50" s="5"/>
-      <c r="AF50" s="5"/>
-      <c r="AG50" s="5"/>
-      <c r="AH50" s="5"/>
-      <c r="AI50" s="5"/>
-      <c r="AJ50" s="5"/>
-      <c r="AK50" s="5"/>
-      <c r="AL50" s="5"/>
-      <c r="AM50" s="5"/>
-      <c r="AO50" s="5"/>
-      <c r="AP50" s="5"/>
-      <c r="AQ50" s="5"/>
-      <c r="AR50" s="5"/>
+    <row r="49" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5">
+        <f t="shared" ref="N49:AD49" si="160">SUM(N41:N48)</f>
+        <v>109297</v>
+      </c>
+      <c r="O49" s="5">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="5">
+        <f t="shared" si="160"/>
+        <v>128469</v>
+      </c>
+      <c r="Q49" s="5">
+        <f t="shared" si="160"/>
+        <v>131620</v>
+      </c>
+      <c r="R49" s="5">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="5">
+        <f t="shared" si="160"/>
+        <v>136662</v>
+      </c>
+      <c r="T49" s="5">
+        <f t="shared" si="160"/>
+        <v>134324</v>
+      </c>
+      <c r="U49" s="5">
+        <f t="shared" si="160"/>
+        <v>137082</v>
+      </c>
+      <c r="V49" s="5">
+        <f t="shared" si="160"/>
+        <v>140976</v>
+      </c>
+      <c r="W49" s="5">
+        <f t="shared" si="160"/>
+        <v>144214</v>
+      </c>
+      <c r="X49" s="5">
+        <f t="shared" si="160"/>
+        <v>148483</v>
+      </c>
+      <c r="Y49" s="5">
+        <f t="shared" si="160"/>
+        <v>161378</v>
+      </c>
+      <c r="Z49" s="5">
+        <f t="shared" si="160"/>
+        <v>168361</v>
+      </c>
+      <c r="AA49" s="5">
+        <f t="shared" si="160"/>
+        <v>180449</v>
+      </c>
+      <c r="AB49" s="5">
+        <f t="shared" si="160"/>
+        <v>0</v>
+      </c>
+      <c r="AC49" s="5">
+        <f t="shared" si="160"/>
+        <v>245240</v>
+      </c>
+      <c r="AD49" s="5">
+        <f t="shared" si="160"/>
+        <v>261759</v>
+      </c>
+      <c r="AE49" s="5"/>
+      <c r="AF49" s="5"/>
+      <c r="AG49" s="5"/>
+      <c r="AH49" s="5"/>
+      <c r="AI49" s="5"/>
+      <c r="AJ49" s="5"/>
+      <c r="AK49" s="5"/>
+      <c r="AL49" s="5"/>
+      <c r="AM49" s="5"/>
+      <c r="AO49" s="5"/>
+      <c r="AP49" s="5"/>
+      <c r="AQ49" s="5"/>
+      <c r="AR49" s="5"/>
     </row>
     <row r="51" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="3" t="s">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -6863,46 +6872,64 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
-        <v>1317</v>
+        <f>3749+72110</f>
+        <v>75859</v>
       </c>
       <c r="O51" s="5"/>
       <c r="P51" s="5">
-        <v>1647</v>
+        <f>81173+9746</f>
+        <v>90919</v>
       </c>
       <c r="Q51" s="5">
-        <v>1610</v>
+        <f>5415+86396</f>
+        <v>91811</v>
       </c>
       <c r="R51" s="5"/>
       <c r="S51" s="5">
-        <v>1034</v>
+        <f>84442+4499</f>
+        <v>88941</v>
       </c>
       <c r="T51" s="5">
-        <v>1107</v>
+        <f>82468+6321</f>
+        <v>88789</v>
       </c>
       <c r="U51" s="5">
-        <v>1658</v>
+        <f>5510+82470</f>
+        <v>87980</v>
       </c>
       <c r="V51" s="5">
-        <v>2357</v>
+        <f>10605+76264</f>
+        <v>86869</v>
       </c>
       <c r="W51" s="5">
-        <v>2207</v>
+        <f>9201+75314</f>
+        <v>84515</v>
       </c>
       <c r="X51" s="5">
-        <v>2679</v>
+        <f>8162+80462</f>
+        <v>88624</v>
       </c>
       <c r="Y51" s="5">
-        <v>2423</v>
+        <f>8167+88109</f>
+        <v>96276</v>
       </c>
       <c r="Z51" s="5">
-        <v>5113</v>
+        <f>7271+85297</f>
+        <v>92568</v>
       </c>
       <c r="AA51" s="5">
-        <v>8203</v>
+        <f>9079+82236</f>
+        <v>91315</v>
       </c>
       <c r="AB51" s="5"/>
-      <c r="AC51" s="5"/>
-      <c r="AD51" s="5"/>
+      <c r="AC51" s="5">
+        <f>9887+124718</f>
+        <v>134605</v>
+      </c>
+      <c r="AD51" s="5">
+        <f>7199+122342</f>
+        <v>129541</v>
+      </c>
       <c r="AE51" s="5"/>
       <c r="AF51" s="5"/>
       <c r="AG51" s="5"/>
@@ -6919,7 +6946,7 @@
     </row>
     <row r="52" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
@@ -6933,46 +6960,50 @@
       <c r="L52" s="5"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
-        <v>1944</v>
+        <v>1317</v>
       </c>
       <c r="O52" s="5"/>
       <c r="P52" s="5">
-        <v>1780</v>
+        <v>1647</v>
       </c>
       <c r="Q52" s="5">
-        <v>1736</v>
+        <v>1610</v>
       </c>
       <c r="R52" s="5"/>
       <c r="S52" s="5">
-        <v>1818</v>
+        <v>1034</v>
       </c>
       <c r="T52" s="5">
-        <v>1706</v>
+        <v>1107</v>
       </c>
       <c r="U52" s="5">
-        <v>1796</v>
+        <v>1658</v>
       </c>
       <c r="V52" s="5">
-        <v>1916</v>
+        <v>2357</v>
       </c>
       <c r="W52" s="5">
-        <v>1772</v>
+        <v>2207</v>
       </c>
       <c r="X52" s="5">
-        <v>1653</v>
+        <v>2679</v>
       </c>
       <c r="Y52" s="5">
-        <v>1839</v>
+        <v>2423</v>
       </c>
       <c r="Z52" s="5">
-        <v>2243</v>
+        <v>5113</v>
       </c>
       <c r="AA52" s="5">
-        <v>1794</v>
+        <v>8203</v>
       </c>
       <c r="AB52" s="5"/>
-      <c r="AC52" s="5"/>
-      <c r="AD52" s="5"/>
+      <c r="AC52" s="5">
+        <v>9474</v>
+      </c>
+      <c r="AD52" s="5">
+        <v>10977</v>
+      </c>
       <c r="AE52" s="5"/>
       <c r="AF52" s="5"/>
       <c r="AG52" s="5"/>
@@ -6989,7 +7020,7 @@
     </row>
     <row r="53" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -7003,46 +7034,50 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
-        <v>8357</v>
+        <v>1944</v>
       </c>
       <c r="O53" s="5"/>
       <c r="P53" s="5">
-        <v>8705</v>
+        <v>1780</v>
       </c>
       <c r="Q53" s="5">
-        <v>8598</v>
+        <v>1736</v>
       </c>
       <c r="R53" s="5"/>
       <c r="S53" s="5">
-        <v>11120</v>
+        <v>1818</v>
       </c>
       <c r="T53" s="5">
-        <v>8878</v>
+        <v>1706</v>
       </c>
       <c r="U53" s="5">
-        <v>8931</v>
+        <v>1796</v>
       </c>
       <c r="V53" s="5">
-        <v>9313</v>
+        <v>1916</v>
       </c>
       <c r="W53" s="5">
-        <v>11455</v>
+        <v>1772</v>
       </c>
       <c r="X53" s="5">
-        <v>9430</v>
+        <v>1653</v>
       </c>
       <c r="Y53" s="5">
-        <v>9019</v>
+        <v>1839</v>
       </c>
       <c r="Z53" s="5">
-        <v>9387</v>
+        <v>2243</v>
       </c>
       <c r="AA53" s="5">
-        <v>12098</v>
+        <v>1794</v>
       </c>
       <c r="AB53" s="5"/>
-      <c r="AC53" s="5"/>
-      <c r="AD53" s="5"/>
+      <c r="AC53" s="5">
+        <v>1940</v>
+      </c>
+      <c r="AD53" s="5">
+        <v>2225</v>
+      </c>
       <c r="AE53" s="5"/>
       <c r="AF53" s="5"/>
       <c r="AG53" s="5"/>
@@ -7059,7 +7094,7 @@
     </row>
     <row r="54" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -7073,46 +7108,50 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
-        <v>4144</v>
+        <v>8357</v>
       </c>
       <c r="O54" s="5"/>
       <c r="P54" s="5">
-        <v>5228</v>
+        <v>8705</v>
       </c>
       <c r="Q54" s="5">
-        <v>5521</v>
+        <v>8598</v>
       </c>
       <c r="R54" s="5"/>
       <c r="S54" s="5">
-        <v>6886</v>
+        <v>11120</v>
       </c>
       <c r="T54" s="5">
-        <v>6395</v>
+        <v>8878</v>
       </c>
       <c r="U54" s="5">
-        <v>6990</v>
+        <v>8931</v>
       </c>
       <c r="V54" s="5">
-        <v>7353</v>
+        <v>9313</v>
       </c>
       <c r="W54" s="5">
-        <v>7410</v>
+        <v>11455</v>
       </c>
       <c r="X54" s="5">
-        <v>7128</v>
+        <v>9430</v>
       </c>
       <c r="Y54" s="5">
-        <v>8175</v>
+        <v>9019</v>
       </c>
       <c r="Z54" s="5">
-        <v>8629</v>
+        <v>9387</v>
       </c>
       <c r="AA54" s="5">
-        <v>8700</v>
+        <v>12098</v>
       </c>
       <c r="AB54" s="5"/>
-      <c r="AC54" s="5"/>
-      <c r="AD54" s="5"/>
+      <c r="AC54" s="5">
+        <v>9881</v>
+      </c>
+      <c r="AD54" s="5">
+        <v>9916</v>
+      </c>
       <c r="AE54" s="5"/>
       <c r="AF54" s="5"/>
       <c r="AG54" s="5"/>
@@ -7129,7 +7168,7 @@
     </row>
     <row r="55" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
@@ -7143,56 +7182,50 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
-        <f>12210+6031</f>
-        <v>18241</v>
+        <v>4144</v>
       </c>
       <c r="O55" s="5"/>
       <c r="P55" s="5">
-        <f>11128+7165</f>
-        <v>18293</v>
+        <v>5228</v>
       </c>
       <c r="Q55" s="5">
-        <f>11335+6814</f>
-        <v>18149</v>
+        <v>5521</v>
       </c>
       <c r="R55" s="5"/>
       <c r="S55" s="5">
-        <f>5281+11201</f>
-        <v>16482</v>
+        <v>6886</v>
       </c>
       <c r="T55" s="5">
-        <f>10046+5244</f>
-        <v>15290</v>
+        <v>6395</v>
       </c>
       <c r="U55" s="5">
-        <f>10451+4483</f>
-        <v>14934</v>
+        <v>6990</v>
       </c>
       <c r="V55" s="5">
-        <f>10817+3692</f>
-        <v>14509</v>
+        <v>7353</v>
       </c>
       <c r="W55" s="5">
-        <f>3442+11038</f>
-        <v>14480</v>
+        <v>7410</v>
       </c>
       <c r="X55" s="5">
-        <f>2864+9553</f>
-        <v>12417</v>
+        <v>7128</v>
       </c>
       <c r="Y55" s="5">
-        <f>2208+9813</f>
-        <v>12021</v>
+        <v>8175</v>
       </c>
       <c r="Z55" s="5">
-        <v>10269</v>
+        <v>8629</v>
       </c>
       <c r="AA55" s="5">
-        <v>10583</v>
+        <v>8700</v>
       </c>
       <c r="AB55" s="5"/>
-      <c r="AC55" s="5"/>
-      <c r="AD55" s="5"/>
+      <c r="AC55" s="5">
+        <v>9555</v>
+      </c>
+      <c r="AD55" s="5">
+        <v>11447</v>
+      </c>
       <c r="AE55" s="5"/>
       <c r="AF55" s="5"/>
       <c r="AG55" s="5"/>
@@ -7209,7 +7242,7 @@
     </row>
     <row r="56" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B56" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
@@ -7223,48 +7256,60 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
-        <v>5203</v>
+        <f>12210+6031</f>
+        <v>18241</v>
       </c>
       <c r="O56" s="5"/>
       <c r="P56" s="5">
-        <v>5673</v>
+        <f>11128+7165</f>
+        <v>18293</v>
       </c>
       <c r="Q56" s="5">
-        <v>6107</v>
+        <f>11335+6814</f>
+        <v>18149</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="5">
-        <v>7540</v>
+        <f>5281+11201</f>
+        <v>16482</v>
       </c>
       <c r="T56" s="5">
-        <v>7781</v>
+        <f>10046+5244</f>
+        <v>15290</v>
       </c>
       <c r="U56" s="5">
-        <v>8611</v>
+        <f>10451+4483</f>
+        <v>14934</v>
       </c>
       <c r="V56" s="5">
-        <v>9420</v>
+        <f>10817+3692</f>
+        <v>14509</v>
       </c>
       <c r="W56" s="5">
-        <v>11106</v>
+        <f>3442+11038</f>
+        <v>14480</v>
       </c>
       <c r="X56" s="5">
-        <v>12316</v>
+        <f>2864+9553</f>
+        <v>12417</v>
       </c>
       <c r="Y56" s="5">
-        <v>14364</v>
+        <f>2208+9813</f>
+        <v>12021</v>
       </c>
       <c r="Z56" s="5">
-        <f>11536+7647</f>
-        <v>19183</v>
+        <v>10269</v>
       </c>
       <c r="AA56" s="5">
-        <f>8996+14094</f>
-        <v>23090</v>
+        <v>10583</v>
       </c>
       <c r="AB56" s="5"/>
-      <c r="AC56" s="5"/>
-      <c r="AD56" s="5"/>
+      <c r="AC56" s="5">
+        <v>11402</v>
+      </c>
+      <c r="AD56" s="5">
+        <v>11771</v>
+      </c>
       <c r="AE56" s="5"/>
       <c r="AF56" s="5"/>
       <c r="AG56" s="5"/>
@@ -7281,7 +7326,7 @@
     </row>
     <row r="57" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B57" s="3" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -7294,48 +7339,27 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="5">
-        <v>-5768</v>
-      </c>
+      <c r="N57" s="5"/>
       <c r="O57" s="5"/>
-      <c r="P57" s="5">
-        <f>-4246+470</f>
-        <v>-3776</v>
-      </c>
-      <c r="Q57" s="5">
-        <v>-1912</v>
-      </c>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
-      <c r="S57" s="5">
-        <v>2841</v>
-      </c>
-      <c r="T57" s="5">
-        <v>4378</v>
-      </c>
-      <c r="U57" s="5">
-        <v>6182</v>
-      </c>
-      <c r="V57" s="5">
-        <v>9239</v>
-      </c>
-      <c r="W57" s="5">
-        <v>11269</v>
-      </c>
-      <c r="X57" s="5">
-        <v>14236</v>
-      </c>
-      <c r="Y57" s="5">
-        <v>17261</v>
-      </c>
-      <c r="Z57" s="5">
-        <v>20969</v>
-      </c>
-      <c r="AA57" s="5">
-        <v>24666</v>
-      </c>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
+      <c r="Z57" s="5"/>
+      <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
-      <c r="AC57" s="5"/>
-      <c r="AD57" s="5"/>
+      <c r="AC57" s="5">
+        <v>18512</v>
+      </c>
+      <c r="AD57" s="5">
+        <v>26648</v>
+      </c>
       <c r="AE57" s="5"/>
       <c r="AF57" s="5"/>
       <c r="AG57" s="5"/>
@@ -7352,7 +7376,7 @@
     </row>
     <row r="58" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B58" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -7366,61 +7390,52 @@
       <c r="L58" s="5"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
-        <f>SUM(N50:N57)</f>
-        <v>109297</v>
-      </c>
-      <c r="O58" s="5">
-        <f>SUM(O50:O57)</f>
-        <v>0</v>
-      </c>
+        <v>5203</v>
+      </c>
+      <c r="O58" s="5"/>
       <c r="P58" s="5">
-        <f>SUM(P50:P57)</f>
-        <v>128469</v>
+        <v>5673</v>
       </c>
       <c r="Q58" s="5">
-        <f>SUM(Q50:Q57)</f>
-        <v>131620</v>
+        <v>6107</v>
       </c>
       <c r="R58" s="5"/>
       <c r="S58" s="5">
-        <f t="shared" ref="S58:AA58" si="163">SUM(S50:S57)</f>
-        <v>136662</v>
+        <v>7540</v>
       </c>
       <c r="T58" s="5">
-        <f t="shared" si="163"/>
-        <v>134324</v>
+        <v>7781</v>
       </c>
       <c r="U58" s="5">
-        <f t="shared" si="163"/>
-        <v>137082</v>
+        <v>8611</v>
       </c>
       <c r="V58" s="5">
-        <f t="shared" si="163"/>
-        <v>140976</v>
+        <v>9420</v>
       </c>
       <c r="W58" s="5">
-        <f t="shared" si="163"/>
-        <v>144214</v>
+        <v>11106</v>
       </c>
       <c r="X58" s="5">
-        <f t="shared" si="163"/>
-        <v>148483</v>
+        <v>12316</v>
       </c>
       <c r="Y58" s="5">
-        <f t="shared" si="163"/>
-        <v>161378</v>
+        <v>14364</v>
       </c>
       <c r="Z58" s="5">
-        <f t="shared" si="163"/>
-        <v>168361</v>
+        <f>11536+7647</f>
+        <v>19183</v>
       </c>
       <c r="AA58" s="5">
-        <f t="shared" si="163"/>
-        <v>180449</v>
+        <f>8996+14094</f>
+        <v>23090</v>
       </c>
       <c r="AB58" s="5"/>
-      <c r="AC58" s="5"/>
-      <c r="AD58" s="5"/>
+      <c r="AC58" s="5">
+        <v>10820</v>
+      </c>
+      <c r="AD58" s="5">
+        <v>16178</v>
+      </c>
       <c r="AE58" s="5"/>
       <c r="AF58" s="5"/>
       <c r="AG58" s="5"/>
@@ -7435,9 +7450,84 @@
       <c r="AQ58" s="5"/>
       <c r="AR58" s="5"/>
     </row>
+    <row r="59" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5">
+        <v>-5768</v>
+      </c>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5">
+        <f>-4246+470</f>
+        <v>-3776</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>-1912</v>
+      </c>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5">
+        <v>2841</v>
+      </c>
+      <c r="T59" s="5">
+        <v>4378</v>
+      </c>
+      <c r="U59" s="5">
+        <v>6182</v>
+      </c>
+      <c r="V59" s="5">
+        <v>9239</v>
+      </c>
+      <c r="W59" s="5">
+        <v>11269</v>
+      </c>
+      <c r="X59" s="5">
+        <v>14236</v>
+      </c>
+      <c r="Y59" s="5">
+        <v>17261</v>
+      </c>
+      <c r="Z59" s="5">
+        <v>20969</v>
+      </c>
+      <c r="AA59" s="5">
+        <v>24666</v>
+      </c>
+      <c r="AB59" s="5"/>
+      <c r="AC59" s="5">
+        <v>39051</v>
+      </c>
+      <c r="AD59" s="5">
+        <v>43056</v>
+      </c>
+      <c r="AE59" s="5"/>
+      <c r="AF59" s="5"/>
+      <c r="AG59" s="5"/>
+      <c r="AH59" s="5"/>
+      <c r="AI59" s="5"/>
+      <c r="AJ59" s="5"/>
+      <c r="AK59" s="5"/>
+      <c r="AL59" s="5"/>
+      <c r="AM59" s="5"/>
+      <c r="AO59" s="5"/>
+      <c r="AP59" s="5"/>
+      <c r="AQ59" s="5"/>
+      <c r="AR59" s="5"/>
+    </row>
     <row r="60" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -7450,50 +7540,71 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
+      <c r="N60" s="5">
+        <f>SUM(N51:N59)</f>
+        <v>109297</v>
+      </c>
+      <c r="O60" s="5">
+        <f>SUM(O51:O59)</f>
+        <v>0</v>
+      </c>
+      <c r="P60" s="5">
+        <f>SUM(P51:P59)</f>
+        <v>128469</v>
+      </c>
+      <c r="Q60" s="5">
+        <f>SUM(Q51:Q59)</f>
+        <v>131620</v>
+      </c>
       <c r="R60" s="5"/>
       <c r="S60" s="5">
-        <f t="shared" ref="S60:V60" si="164">+S29</f>
-        <v>2509</v>
+        <f t="shared" ref="S60:AD60" si="161">SUM(S51:S59)</f>
+        <v>136662</v>
       </c>
       <c r="T60" s="5">
-        <f t="shared" si="164"/>
-        <v>2733</v>
+        <f t="shared" si="161"/>
+        <v>134324</v>
       </c>
       <c r="U60" s="5">
-        <f t="shared" si="164"/>
-        <v>2934</v>
+        <f t="shared" si="161"/>
+        <v>137082</v>
       </c>
       <c r="V60" s="5">
-        <f t="shared" si="164"/>
-        <v>3562</v>
+        <f t="shared" si="161"/>
+        <v>140976</v>
       </c>
       <c r="W60" s="5">
-        <f>+W29</f>
-        <v>2957</v>
+        <f t="shared" si="161"/>
+        <v>144214</v>
       </c>
       <c r="X60" s="5">
-        <f t="shared" ref="X60:AA60" si="165">+X29</f>
-        <v>3857</v>
+        <f t="shared" si="161"/>
+        <v>148483</v>
       </c>
       <c r="Y60" s="5">
-        <f t="shared" si="165"/>
-        <v>3575</v>
+        <f t="shared" si="161"/>
+        <v>161378</v>
       </c>
       <c r="Z60" s="5">
-        <f t="shared" si="165"/>
-        <v>4034</v>
+        <f t="shared" si="161"/>
+        <v>168361</v>
       </c>
       <c r="AA60" s="5">
-        <f t="shared" si="165"/>
-        <v>3689</v>
-      </c>
-      <c r="AB60" s="5"/>
-      <c r="AC60" s="5"/>
-      <c r="AD60" s="5"/>
+        <f t="shared" si="161"/>
+        <v>180449</v>
+      </c>
+      <c r="AB60" s="5">
+        <f t="shared" si="161"/>
+        <v>0</v>
+      </c>
+      <c r="AC60" s="5">
+        <f t="shared" si="161"/>
+        <v>245240</v>
+      </c>
+      <c r="AD60" s="5">
+        <f t="shared" si="161"/>
+        <v>261759</v>
+      </c>
       <c r="AE60" s="5"/>
       <c r="AF60" s="5"/>
       <c r="AG60" s="5"/>
@@ -7506,86 +7617,11 @@
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
       <c r="AQ60" s="5"/>
-      <c r="AR60" s="5">
-        <f>+AR29</f>
-        <v>13293</v>
-      </c>
-    </row>
-    <row r="61" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
-      <c r="R61" s="5"/>
-      <c r="S61" s="5">
-        <v>2420</v>
-      </c>
-      <c r="T61" s="5">
-        <f>4923-S61</f>
-        <v>2503</v>
-      </c>
-      <c r="U61" s="5">
-        <f>7323-T61-S61</f>
-        <v>2400</v>
-      </c>
-      <c r="V61" s="5">
-        <f>10467-U61-T61-S61</f>
-        <v>3144</v>
-      </c>
-      <c r="W61" s="5">
-        <v>2929</v>
-      </c>
-      <c r="X61" s="5">
-        <f>6080-W61</f>
-        <v>3151</v>
-      </c>
-      <c r="Y61" s="5">
-        <f>9016-X61-W61</f>
-        <v>2936</v>
-      </c>
-      <c r="Z61" s="5">
-        <f>12443-Y61-X61-W61</f>
-        <v>3427</v>
-      </c>
-      <c r="AA61" s="5">
-        <v>2927</v>
-      </c>
-      <c r="AB61" s="5"/>
-      <c r="AC61" s="5"/>
-      <c r="AD61" s="5"/>
-      <c r="AE61" s="5"/>
-      <c r="AF61" s="5"/>
-      <c r="AG61" s="5"/>
-      <c r="AH61" s="5"/>
-      <c r="AI61" s="5"/>
-      <c r="AJ61" s="5"/>
-      <c r="AK61" s="5"/>
-      <c r="AL61" s="5"/>
-      <c r="AM61" s="5"/>
-      <c r="AO61" s="5"/>
-      <c r="AP61" s="5"/>
-      <c r="AQ61" s="5"/>
-      <c r="AR61" s="5">
-        <v>6717</v>
-      </c>
+      <c r="AR60" s="5"/>
     </row>
     <row r="62" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -7604,37 +7640,40 @@
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5">
-        <v>712</v>
+        <f t="shared" ref="S62:V62" si="162">+S29</f>
+        <v>2509</v>
       </c>
       <c r="T62" s="5">
-        <f>1510-S62</f>
-        <v>798</v>
+        <f t="shared" si="162"/>
+        <v>2733</v>
       </c>
       <c r="U62" s="5">
-        <f>2318-T62-S62</f>
-        <v>808</v>
+        <f t="shared" si="162"/>
+        <v>2934</v>
       </c>
       <c r="V62" s="5">
-        <f>3129-U62-T62-S62</f>
-        <v>811</v>
+        <f t="shared" si="162"/>
+        <v>3562</v>
       </c>
       <c r="W62" s="5">
-        <v>804</v>
+        <f>+W29</f>
+        <v>2957</v>
       </c>
       <c r="X62" s="5">
-        <f>1712-W62</f>
-        <v>908</v>
+        <f t="shared" ref="X62:AA62" si="163">+X29</f>
+        <v>3857</v>
       </c>
       <c r="Y62" s="5">
-        <f>2715-X62-W62</f>
-        <v>1003</v>
+        <f t="shared" si="163"/>
+        <v>3575</v>
       </c>
       <c r="Z62" s="5">
-        <f>3867-Y62-X62-W62</f>
-        <v>1152</v>
+        <f t="shared" si="163"/>
+        <v>4034</v>
       </c>
       <c r="AA62" s="5">
-        <v>1351</v>
+        <f t="shared" si="163"/>
+        <v>3689</v>
       </c>
       <c r="AB62" s="5"/>
       <c r="AC62" s="5"/>
@@ -7652,12 +7691,13 @@
       <c r="AP62" s="5"/>
       <c r="AQ62" s="5"/>
       <c r="AR62" s="5">
-        <v>1972</v>
+        <f>+AR29</f>
+        <v>13293</v>
       </c>
     </row>
     <row r="63" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -7676,37 +7716,37 @@
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5">
-        <v>763</v>
+        <v>2420</v>
       </c>
       <c r="T63" s="5">
-        <f>1518-S63</f>
-        <v>755</v>
+        <f>4923-S63</f>
+        <v>2503</v>
       </c>
       <c r="U63" s="5">
-        <f>2267-T63-S63</f>
-        <v>749</v>
+        <f>7323-T63-S63</f>
+        <v>2400</v>
       </c>
       <c r="V63" s="5">
-        <f>3010-U63-T63-S63</f>
-        <v>743</v>
+        <f>10467-U63-T63-S63</f>
+        <v>3144</v>
       </c>
       <c r="W63" s="5">
-        <v>624</v>
+        <v>2929</v>
       </c>
       <c r="X63" s="5">
-        <f>1215-W63</f>
-        <v>591</v>
+        <f>6080-W63</f>
+        <v>3151</v>
       </c>
       <c r="Y63" s="5">
-        <f>1763-X63-W63</f>
-        <v>548</v>
+        <f>9016-X63-W63</f>
+        <v>2936</v>
       </c>
       <c r="Z63" s="5">
-        <f>2307-Y63-X63-W63</f>
-        <v>544</v>
+        <f>12443-Y63-X63-W63</f>
+        <v>3427</v>
       </c>
       <c r="AA63" s="5">
-        <v>420</v>
+        <v>2927</v>
       </c>
       <c r="AB63" s="5"/>
       <c r="AC63" s="5"/>
@@ -7724,12 +7764,12 @@
       <c r="AP63" s="5"/>
       <c r="AQ63" s="5"/>
       <c r="AR63" s="5">
-        <v>1150</v>
+        <v>6717</v>
       </c>
     </row>
     <row r="64" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -7748,37 +7788,37 @@
       <c r="Q64" s="5"/>
       <c r="R64" s="5"/>
       <c r="S64" s="5">
-        <v>-517</v>
+        <v>712</v>
       </c>
       <c r="T64" s="5">
-        <f>-1049-S64</f>
-        <v>-532</v>
+        <f>1510-S64</f>
+        <v>798</v>
       </c>
       <c r="U64" s="5">
-        <f>-1755-T64-S64</f>
-        <v>-706</v>
+        <f>2318-T64-S64</f>
+        <v>808</v>
       </c>
       <c r="V64" s="5">
-        <f>-2139-U64-T64-S64</f>
-        <v>-384</v>
+        <f>3129-U64-T64-S64</f>
+        <v>811</v>
       </c>
       <c r="W64" s="5">
-        <v>-151</v>
+        <v>804</v>
       </c>
       <c r="X64" s="5">
-        <f>-601-W64</f>
-        <v>-450</v>
+        <f>1712-W64</f>
+        <v>908</v>
       </c>
       <c r="Y64" s="5">
-        <f>-1097-X64-W64</f>
-        <v>-496</v>
+        <f>2715-X64-W64</f>
+        <v>1003</v>
       </c>
       <c r="Z64" s="5">
-        <f>-1637-Y64-X64-W64</f>
-        <v>-540</v>
+        <f>3867-Y64-X64-W64</f>
+        <v>1152</v>
       </c>
       <c r="AA64" s="5">
-        <v>515</v>
+        <v>1351</v>
       </c>
       <c r="AB64" s="5"/>
       <c r="AC64" s="5"/>
@@ -7796,12 +7836,12 @@
       <c r="AP64" s="5"/>
       <c r="AQ64" s="5"/>
       <c r="AR64" s="5">
-        <v>-1146</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="65" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -7820,37 +7860,37 @@
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5">
-        <v>849</v>
+        <v>763</v>
       </c>
       <c r="T65" s="5">
-        <f>1878-S65</f>
-        <v>1029</v>
+        <f>1518-S65</f>
+        <v>755</v>
       </c>
       <c r="U65" s="5">
-        <f>2927-T65-S65</f>
-        <v>1049</v>
+        <f>2267-T65-S65</f>
+        <v>749</v>
       </c>
       <c r="V65" s="5">
-        <f>3974-U65-T65-S65</f>
-        <v>1047</v>
+        <f>3010-U65-T65-S65</f>
+        <v>743</v>
       </c>
       <c r="W65" s="5">
-        <v>1007</v>
+        <v>624</v>
       </c>
       <c r="X65" s="5">
-        <f>2176-W65</f>
-        <v>1169</v>
+        <f>1215-W65</f>
+        <v>591</v>
       </c>
       <c r="Y65" s="5">
-        <f>3374-X65-W65</f>
-        <v>1198</v>
+        <f>1763-X65-W65</f>
+        <v>548</v>
       </c>
       <c r="Z65" s="5">
-        <f>4674-Y65-X65-W65</f>
-        <v>1300</v>
+        <f>2307-Y65-X65-W65</f>
+        <v>544</v>
       </c>
       <c r="AA65" s="5">
-        <v>1124</v>
+        <v>420</v>
       </c>
       <c r="AB65" s="5"/>
       <c r="AC65" s="5"/>
@@ -7868,12 +7908,12 @@
       <c r="AP65" s="5"/>
       <c r="AQ65" s="5"/>
       <c r="AR65" s="5">
-        <v>2613</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="66" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -7892,37 +7932,37 @@
       <c r="Q66" s="5"/>
       <c r="R66" s="5"/>
       <c r="S66" s="5">
-        <v>169</v>
+        <v>-517</v>
       </c>
       <c r="T66" s="5">
-        <f>331-S66</f>
-        <v>162</v>
+        <f>-1049-S66</f>
+        <v>-532</v>
       </c>
       <c r="U66" s="5">
-        <f>631-T66-S66</f>
-        <v>300</v>
+        <f>-1755-T66-S66</f>
+        <v>-706</v>
       </c>
       <c r="V66" s="5">
-        <f>720-U66-T66-S66</f>
-        <v>89</v>
+        <f>-2139-U66-T66-S66</f>
+        <v>-384</v>
       </c>
       <c r="W66" s="5">
-        <v>130</v>
+        <v>-151</v>
       </c>
       <c r="X66" s="5">
-        <f>298-W66</f>
-        <v>168</v>
+        <f>-601-W66</f>
+        <v>-450</v>
       </c>
       <c r="Y66" s="5">
-        <f>422-X66-W66</f>
-        <v>124</v>
+        <f>-1097-X66-W66</f>
+        <v>-496</v>
       </c>
       <c r="Z66" s="5">
-        <f>667-Y66-X66-W66</f>
-        <v>245</v>
+        <f>-1637-Y66-X66-W66</f>
+        <v>-540</v>
       </c>
       <c r="AA66" s="5">
-        <v>164</v>
+        <v>515</v>
       </c>
       <c r="AB66" s="5"/>
       <c r="AC66" s="5"/>
@@ -7940,12 +7980,12 @@
       <c r="AP66" s="5"/>
       <c r="AQ66" s="5"/>
       <c r="AR66" s="5">
-        <v>220</v>
+        <v>-1146</v>
       </c>
     </row>
     <row r="67" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -7964,40 +8004,37 @@
       <c r="Q67" s="5"/>
       <c r="R67" s="5"/>
       <c r="S67" s="5">
-        <f>380+269-457+69+2317</f>
-        <v>2578</v>
+        <v>849</v>
       </c>
       <c r="T67" s="5">
-        <f>145+301-1048-1541+149-S67</f>
-        <v>-4572</v>
+        <f>1878-S67</f>
+        <v>1029</v>
       </c>
       <c r="U67" s="5">
-        <f>-409+457-682-788+303-T67-S67</f>
-        <v>875</v>
+        <f>2927-T67-S67</f>
+        <v>1049</v>
       </c>
       <c r="V67" s="5">
-        <f>-965+542-594-127+656-U67-T67-S67</f>
-        <v>631</v>
+        <f>3974-U67-T67-S67</f>
+        <v>1047</v>
       </c>
       <c r="W67" s="5">
-        <f>-81+367-531+24+2305</f>
-        <v>2084</v>
+        <v>1007</v>
       </c>
       <c r="X67" s="5">
-        <f>-451+676-1143-1685+454-W67</f>
-        <v>-4233</v>
+        <f>2176-W67</f>
+        <v>1169</v>
       </c>
       <c r="Y67" s="5">
-        <f>-312+603-633-1222+35-X67-W67</f>
-        <v>620</v>
+        <f>3374-X67-W67</f>
+        <v>1198</v>
       </c>
       <c r="Z67" s="5">
-        <f>-653+266-608-659+154-Y67-X67-W67</f>
-        <v>29</v>
+        <f>4674-Y67-X67-W67</f>
+        <v>1300</v>
       </c>
       <c r="AA67" s="5">
-        <f>-245+59-334-391+2550</f>
-        <v>1639</v>
+        <v>1124</v>
       </c>
       <c r="AB67" s="5"/>
       <c r="AC67" s="5"/>
@@ -8015,13 +8052,12 @@
       <c r="AP67" s="5"/>
       <c r="AQ67" s="5"/>
       <c r="AR67" s="5">
-        <f>-874+11-733-398+7</f>
-        <v>-1987</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="68" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -8040,40 +8076,37 @@
       <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
       <c r="S68" s="5">
-        <f t="shared" ref="S68:V68" si="166">SUM(S61:S67)</f>
-        <v>6974</v>
+        <v>169</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="166"/>
-        <v>143</v>
+        <f>331-S68</f>
+        <v>162</v>
       </c>
       <c r="U68" s="5">
-        <f t="shared" si="166"/>
-        <v>5475</v>
+        <f>631-T68-S68</f>
+        <v>300</v>
       </c>
       <c r="V68" s="5">
-        <f t="shared" si="166"/>
-        <v>6081</v>
+        <f>720-U68-T68-S68</f>
+        <v>89</v>
       </c>
       <c r="W68" s="5">
-        <f>SUM(W61:W67)</f>
-        <v>7427</v>
+        <v>130</v>
       </c>
       <c r="X68" s="5">
-        <f t="shared" ref="X68:AA68" si="167">SUM(X61:X67)</f>
-        <v>1304</v>
+        <f>298-W68</f>
+        <v>168</v>
       </c>
       <c r="Y68" s="5">
-        <f t="shared" si="167"/>
-        <v>5933</v>
+        <f>422-X68-W68</f>
+        <v>124</v>
       </c>
       <c r="Z68" s="5">
-        <f t="shared" si="167"/>
-        <v>6157</v>
+        <f>667-Y68-X68-W68</f>
+        <v>245</v>
       </c>
       <c r="AA68" s="5">
-        <f t="shared" si="167"/>
-        <v>8140</v>
+        <v>164</v>
       </c>
       <c r="AB68" s="5"/>
       <c r="AC68" s="5"/>
@@ -8088,20 +8121,91 @@
       <c r="AL68" s="5"/>
       <c r="AM68" s="5"/>
       <c r="AO68" s="5"/>
-      <c r="AP68" s="5">
-        <v>13139</v>
-      </c>
-      <c r="AQ68" s="5">
-        <v>15887</v>
-      </c>
+      <c r="AP68" s="5"/>
+      <c r="AQ68" s="5"/>
       <c r="AR68" s="5">
-        <f>SUM(AR61:AR67)</f>
-        <v>9539</v>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5">
+        <f>380+269-457+69+2317</f>
+        <v>2578</v>
+      </c>
+      <c r="T69" s="5">
+        <f>145+301-1048-1541+149-S69</f>
+        <v>-4572</v>
+      </c>
+      <c r="U69" s="5">
+        <f>-409+457-682-788+303-T69-S69</f>
+        <v>875</v>
+      </c>
+      <c r="V69" s="5">
+        <f>-965+542-594-127+656-U69-T69-S69</f>
+        <v>631</v>
+      </c>
+      <c r="W69" s="5">
+        <f>-81+367-531+24+2305</f>
+        <v>2084</v>
+      </c>
+      <c r="X69" s="5">
+        <f>-451+676-1143-1685+454-W69</f>
+        <v>-4233</v>
+      </c>
+      <c r="Y69" s="5">
+        <f>-312+603-633-1222+35-X69-W69</f>
+        <v>620</v>
+      </c>
+      <c r="Z69" s="5">
+        <f>-653+266-608-659+154-Y69-X69-W69</f>
+        <v>29</v>
+      </c>
+      <c r="AA69" s="5">
+        <f>-245+59-334-391+2550</f>
+        <v>1639</v>
+      </c>
+      <c r="AB69" s="5"/>
+      <c r="AC69" s="5"/>
+      <c r="AD69" s="5"/>
+      <c r="AE69" s="5"/>
+      <c r="AF69" s="5"/>
+      <c r="AG69" s="5"/>
+      <c r="AH69" s="5"/>
+      <c r="AI69" s="5"/>
+      <c r="AJ69" s="5"/>
+      <c r="AK69" s="5"/>
+      <c r="AL69" s="5"/>
+      <c r="AM69" s="5"/>
+      <c r="AO69" s="5"/>
+      <c r="AP69" s="5"/>
+      <c r="AQ69" s="5"/>
+      <c r="AR69" s="5">
+        <f>-874+11-733-398+7</f>
+        <v>-1987</v>
       </c>
     </row>
     <row r="70" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -8120,37 +8224,40 @@
       <c r="Q70" s="5"/>
       <c r="R70" s="5"/>
       <c r="S70" s="5">
-        <v>-1314</v>
+        <f t="shared" ref="S70:V70" si="164">SUM(S63:S69)</f>
+        <v>6974</v>
       </c>
       <c r="T70" s="5">
-        <f>-2394-S70</f>
-        <v>-1080</v>
+        <f t="shared" si="164"/>
+        <v>143</v>
       </c>
       <c r="U70" s="5">
-        <f>-4068-T70-S70</f>
-        <v>-1674</v>
+        <f t="shared" si="164"/>
+        <v>5475</v>
       </c>
       <c r="V70" s="5">
-        <f>-6866-U70-T70-S70</f>
-        <v>-2798</v>
+        <f t="shared" si="164"/>
+        <v>6081</v>
       </c>
       <c r="W70" s="5">
-        <v>-2303</v>
+        <f>SUM(W63:W69)</f>
+        <v>7427</v>
       </c>
       <c r="X70" s="5">
-        <f>-6273-W70</f>
-        <v>-3970</v>
+        <f t="shared" ref="X70:AA70" si="165">SUM(X63:X69)</f>
+        <v>1304</v>
       </c>
       <c r="Y70" s="5">
-        <f>-12135-X70-W70</f>
-        <v>-5862</v>
+        <f t="shared" si="165"/>
+        <v>5933</v>
       </c>
       <c r="Z70" s="5">
-        <f>-21215-Y70-X70-W70</f>
-        <v>-9080</v>
+        <f t="shared" si="165"/>
+        <v>6157</v>
       </c>
       <c r="AA70" s="5">
-        <v>-8502</v>
+        <f t="shared" si="165"/>
+        <v>8140</v>
       </c>
       <c r="AB70" s="5"/>
       <c r="AC70" s="5"/>
@@ -8166,87 +8273,19 @@
       <c r="AM70" s="5"/>
       <c r="AO70" s="5"/>
       <c r="AP70" s="5">
-        <v>-1564</v>
+        <v>13139</v>
       </c>
       <c r="AQ70" s="5">
-        <v>-2135</v>
+        <v>15887</v>
       </c>
       <c r="AR70" s="5">
-        <v>-4511</v>
-      </c>
-    </row>
-    <row r="71" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5">
-        <v>0</v>
-      </c>
-      <c r="T71" s="5">
-        <f>-59-S71</f>
-        <v>-59</v>
-      </c>
-      <c r="U71" s="5">
-        <f>-59-T71-S71</f>
-        <v>0</v>
-      </c>
-      <c r="V71" s="5">
-        <f>-63-U71-T71-S71</f>
-        <v>-4</v>
-      </c>
-      <c r="W71" s="5">
-        <v>0</v>
-      </c>
-      <c r="X71" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z71" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="5"/>
-      <c r="AC71" s="5"/>
-      <c r="AD71" s="5"/>
-      <c r="AE71" s="5"/>
-      <c r="AF71" s="5"/>
-      <c r="AG71" s="5"/>
-      <c r="AH71" s="5"/>
-      <c r="AI71" s="5"/>
-      <c r="AJ71" s="5"/>
-      <c r="AK71" s="5"/>
-      <c r="AL71" s="5"/>
-      <c r="AM71" s="5"/>
-      <c r="AO71" s="5"/>
-      <c r="AP71" s="5"/>
-      <c r="AQ71" s="5"/>
-      <c r="AR71" s="5">
-        <v>-148</v>
+        <f>SUM(AR63:AR69)</f>
+        <v>9539</v>
       </c>
     </row>
     <row r="72" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
@@ -8265,40 +8304,37 @@
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="5">
-        <f>-333+85</f>
-        <v>-248</v>
+        <v>-1314</v>
       </c>
       <c r="T72" s="5">
-        <f>-515+157-S72</f>
-        <v>-110</v>
+        <f>-2394-S72</f>
+        <v>-1080</v>
       </c>
       <c r="U72" s="5">
-        <f>-674+207-T72-S72</f>
-        <v>-109</v>
+        <f>-4068-T72-S72</f>
+        <v>-1674</v>
       </c>
       <c r="V72" s="5">
-        <f>-1003+572-U72-T72-S72</f>
-        <v>36</v>
+        <f>-6866-U72-T72-S72</f>
+        <v>-2798</v>
       </c>
       <c r="W72" s="5">
-        <f>15-477</f>
-        <v>-462</v>
+        <v>-2303</v>
       </c>
       <c r="X72" s="5">
-        <f>356-636-W72</f>
-        <v>182</v>
+        <f>-6273-W72</f>
+        <v>-3970</v>
       </c>
       <c r="Y72" s="5">
-        <f>-838+444-X72-W72</f>
-        <v>-114</v>
+        <f>-12135-X72-W72</f>
+        <v>-5862</v>
       </c>
       <c r="Z72" s="5">
-        <f>-1272+776-Y72-X72-W72</f>
-        <v>-102</v>
+        <f>-21215-Y72-X72-W72</f>
+        <v>-9080</v>
       </c>
       <c r="AA72" s="5">
-        <f>-471+255</f>
-        <v>-216</v>
+        <v>-8502</v>
       </c>
       <c r="AB72" s="5"/>
       <c r="AC72" s="5"/>
@@ -8313,13 +8349,19 @@
       <c r="AL72" s="5"/>
       <c r="AM72" s="5"/>
       <c r="AO72" s="5"/>
-      <c r="AP72" s="5"/>
-      <c r="AQ72" s="5"/>
-      <c r="AR72" s="5"/>
+      <c r="AP72" s="5">
+        <v>-1564</v>
+      </c>
+      <c r="AQ72" s="5">
+        <v>-2135</v>
+      </c>
+      <c r="AR72" s="5">
+        <v>-4511</v>
+      </c>
     </row>
     <row r="73" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="3" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
@@ -8338,40 +8380,34 @@
       <c r="Q73" s="5"/>
       <c r="R73" s="5"/>
       <c r="S73" s="5">
-        <f t="shared" ref="S73:AA73" si="168">SUM(S70:S72)</f>
-        <v>-1562</v>
+        <v>0</v>
       </c>
       <c r="T73" s="5">
-        <f t="shared" si="168"/>
-        <v>-1249</v>
+        <f>-59-S73</f>
+        <v>-59</v>
       </c>
       <c r="U73" s="5">
-        <f t="shared" si="168"/>
-        <v>-1783</v>
+        <f>-59-T73-S73</f>
+        <v>0</v>
       </c>
       <c r="V73" s="5">
-        <f t="shared" si="168"/>
-        <v>-2766</v>
+        <f>-63-U73-T73-S73</f>
+        <v>-4</v>
       </c>
       <c r="W73" s="5">
-        <f t="shared" si="168"/>
-        <v>-2765</v>
+        <v>0</v>
       </c>
       <c r="X73" s="5">
-        <f t="shared" si="168"/>
-        <v>-3788</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="5">
-        <f t="shared" si="168"/>
-        <v>-5976</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="5">
-        <f t="shared" si="168"/>
-        <v>-9182</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="5">
-        <f t="shared" si="168"/>
-        <v>-8718</v>
+        <v>0</v>
       </c>
       <c r="AB73" s="5"/>
       <c r="AC73" s="5"/>
@@ -8388,9 +8424,14 @@
       <c r="AO73" s="5"/>
       <c r="AP73" s="5"/>
       <c r="AQ73" s="5"/>
-      <c r="AR73" s="5"/>
+      <c r="AR73" s="5">
+        <v>-148</v>
+      </c>
     </row>
     <row r="74" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
@@ -8407,15 +8448,42 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
       <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" s="5"/>
-      <c r="W74" s="5"/>
-      <c r="X74" s="5"/>
-      <c r="Y74" s="5"/>
-      <c r="Z74" s="5"/>
-      <c r="AA74" s="5"/>
+      <c r="S74" s="5">
+        <f>-333+85</f>
+        <v>-248</v>
+      </c>
+      <c r="T74" s="5">
+        <f>-515+157-S74</f>
+        <v>-110</v>
+      </c>
+      <c r="U74" s="5">
+        <f>-674+207-T74-S74</f>
+        <v>-109</v>
+      </c>
+      <c r="V74" s="5">
+        <f>-1003+572-U74-T74-S74</f>
+        <v>36</v>
+      </c>
+      <c r="W74" s="5">
+        <f>15-477</f>
+        <v>-462</v>
+      </c>
+      <c r="X74" s="5">
+        <f>356-636-W74</f>
+        <v>182</v>
+      </c>
+      <c r="Y74" s="5">
+        <f>-838+444-X74-W74</f>
+        <v>-114</v>
+      </c>
+      <c r="Z74" s="5">
+        <f>-1272+776-Y74-X74-W74</f>
+        <v>-102</v>
+      </c>
+      <c r="AA74" s="5">
+        <f>-471+255</f>
+        <v>-216</v>
+      </c>
       <c r="AB74" s="5"/>
       <c r="AC74" s="5"/>
       <c r="AD74" s="5"/>
@@ -8435,7 +8503,7 @@
     </row>
     <row r="75" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -8454,40 +8522,40 @@
       <c r="Q75" s="5"/>
       <c r="R75" s="5"/>
       <c r="S75" s="5">
-        <f>-150+308-1060</f>
-        <v>-902</v>
+        <f t="shared" ref="S75:AA75" si="166">SUM(S72:S74)</f>
+        <v>-1562</v>
       </c>
       <c r="T75" s="5">
-        <f>-600+426-1733-S75</f>
-        <v>-1005</v>
+        <f t="shared" si="166"/>
+        <v>-1249</v>
       </c>
       <c r="U75" s="5">
-        <f>-1050+454-1865-T75-S75</f>
-        <v>-554</v>
+        <f t="shared" si="166"/>
+        <v>-1783</v>
       </c>
       <c r="V75" s="5">
-        <f>-1202+742-2040-U75-T75-S75</f>
-        <v>-39</v>
+        <f t="shared" si="166"/>
+        <v>-2766</v>
       </c>
       <c r="W75" s="5">
-        <f>-150+179-851</f>
-        <v>-822</v>
+        <f t="shared" si="166"/>
+        <v>-2765</v>
       </c>
       <c r="X75" s="5">
-        <f>-300+307-898-W75</f>
-        <v>-69</v>
+        <f t="shared" si="166"/>
+        <v>-3788</v>
       </c>
       <c r="Y75" s="5">
-        <f>-450+520-900-X75-W75</f>
-        <v>61</v>
+        <f t="shared" si="166"/>
+        <v>-5976</v>
       </c>
       <c r="Z75" s="5">
-        <f>-600+653-900-Y75-X75-W75</f>
-        <v>-17</v>
+        <f t="shared" si="166"/>
+        <v>-9182</v>
       </c>
       <c r="AA75" s="5">
-        <f>-95+1170-17</f>
-        <v>1058</v>
+        <f t="shared" si="166"/>
+        <v>-8718</v>
       </c>
       <c r="AB75" s="5"/>
       <c r="AC75" s="5"/>
@@ -8507,9 +8575,6 @@
       <c r="AR75" s="5"/>
     </row>
     <row r="76" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -8526,39 +8591,15 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="5"/>
-      <c r="S76" s="5">
-        <v>-1091</v>
-      </c>
-      <c r="T76" s="5">
-        <f>-2190-S76</f>
-        <v>-1099</v>
-      </c>
-      <c r="U76" s="5">
-        <f>-3289-T76-S76</f>
-        <v>-1099</v>
-      </c>
-      <c r="V76" s="5">
-        <f>-4391-U76-T76-S76</f>
-        <v>-1102</v>
-      </c>
-      <c r="W76" s="5">
-        <v>-1103</v>
-      </c>
-      <c r="X76" s="5">
-        <f>-2221-W76</f>
-        <v>-1118</v>
-      </c>
-      <c r="Y76" s="5">
-        <f>-3340-X76-W76</f>
-        <v>-1119</v>
-      </c>
-      <c r="Z76" s="5">
-        <f>-4743-Y76-X76-W76</f>
-        <v>-1403</v>
-      </c>
-      <c r="AA76" s="5">
-        <v>-1413</v>
-      </c>
+      <c r="S76" s="5"/>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+      <c r="V76" s="5"/>
+      <c r="W76" s="5"/>
+      <c r="X76" s="5"/>
+      <c r="Y76" s="5"/>
+      <c r="Z76" s="5"/>
+      <c r="AA76" s="5"/>
       <c r="AB76" s="5"/>
       <c r="AC76" s="5"/>
       <c r="AD76" s="5"/>
@@ -8578,7 +8619,7 @@
     </row>
     <row r="77" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="3" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -8597,40 +8638,40 @@
       <c r="Q77" s="5"/>
       <c r="R77" s="5"/>
       <c r="S77" s="5">
-        <f>-562-1000</f>
-        <v>-1562</v>
+        <f>-150+308-1060</f>
+        <v>-902</v>
       </c>
       <c r="T77" s="5">
-        <f>1749-3500-S77</f>
-        <v>-189</v>
+        <f>-600+426-1733-S77</f>
+        <v>-1005</v>
       </c>
       <c r="U77" s="5">
-        <f>936-3500-T77-S77</f>
-        <v>-813</v>
+        <f>-1050+454-1865-T77-S77</f>
+        <v>-554</v>
       </c>
       <c r="V77" s="5">
-        <f>-167-3500+4-U77-T77-S77</f>
-        <v>-1099</v>
+        <f>-1202+742-2040-U77-T77-S77</f>
+        <v>-39</v>
       </c>
       <c r="W77" s="5">
-        <f>-396+5627-7630</f>
-        <v>-2399</v>
+        <f>-150+179-851</f>
+        <v>-822</v>
       </c>
       <c r="X77" s="5">
-        <f>-396+11837-9700-W77</f>
-        <v>4140</v>
+        <f>-300+307-898-W77</f>
+        <v>-69</v>
       </c>
       <c r="Y77" s="5">
-        <f>-396+19548-9771-X77-W77</f>
-        <v>7640</v>
+        <f>-450+520-900-X77-W77</f>
+        <v>61</v>
       </c>
       <c r="Z77" s="5">
-        <f>1889+19548-15841-Y77-X77-W77</f>
-        <v>-3785</v>
+        <f>-600+653-900-Y77-X77-W77</f>
+        <v>-17</v>
       </c>
       <c r="AA77" s="5">
-        <f>-238-1052</f>
-        <v>-1290</v>
+        <f>-95+1170-17</f>
+        <v>1058</v>
       </c>
       <c r="AB77" s="5"/>
       <c r="AC77" s="5"/>
@@ -8651,7 +8692,7 @@
     </row>
     <row r="78" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="3" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -8670,37 +8711,37 @@
       <c r="Q78" s="5"/>
       <c r="R78" s="5"/>
       <c r="S78" s="5">
-        <v>27</v>
+        <v>-1091</v>
       </c>
       <c r="T78" s="5">
-        <f>31-S78</f>
-        <v>4</v>
+        <f>-2190-S78</f>
+        <v>-1099</v>
       </c>
       <c r="U78" s="5">
-        <f>34-T78-S78</f>
-        <v>3</v>
+        <f>-3289-T78-S78</f>
+        <v>-1099</v>
       </c>
       <c r="V78" s="5">
-        <f>0-U78-T78-S78</f>
-        <v>-34</v>
+        <f>-4391-U78-T78-S78</f>
+        <v>-1102</v>
       </c>
       <c r="W78" s="5">
-        <v>-261</v>
+        <v>-1103</v>
       </c>
       <c r="X78" s="5">
-        <f>-276-W78</f>
-        <v>-15</v>
+        <f>-2221-W78</f>
+        <v>-1118</v>
       </c>
       <c r="Y78" s="5">
-        <f>-299-X78-W78</f>
-        <v>-23</v>
+        <f>-3340-X78-W78</f>
+        <v>-1119</v>
       </c>
       <c r="Z78" s="5">
-        <f>1092-Y78-X78-W78</f>
-        <v>1391</v>
+        <f>-4743-Y78-X78-W78</f>
+        <v>-1403</v>
       </c>
       <c r="AA78" s="5">
-        <v>1855</v>
+        <v>-1413</v>
       </c>
       <c r="AB78" s="5"/>
       <c r="AC78" s="5"/>
@@ -8721,7 +8762,7 @@
     </row>
     <row r="79" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="3" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
@@ -8740,40 +8781,40 @@
       <c r="Q79" s="5"/>
       <c r="R79" s="5"/>
       <c r="S79" s="5">
-        <f>SUM(S75:S78)</f>
-        <v>-3528</v>
+        <f>-562-1000</f>
+        <v>-1562</v>
       </c>
       <c r="T79" s="5">
-        <f>SUM(T75:T78)</f>
-        <v>-2289</v>
+        <f>1749-3500-S79</f>
+        <v>-189</v>
       </c>
       <c r="U79" s="5">
-        <f>SUM(U75:U78)</f>
-        <v>-2463</v>
+        <f>936-3500-T79-S79</f>
+        <v>-813</v>
       </c>
       <c r="V79" s="5">
-        <f>SUM(V75:V78)</f>
-        <v>-2274</v>
+        <f>-167-3500+4-U79-T79-S79</f>
+        <v>-1099</v>
       </c>
       <c r="W79" s="5">
-        <f>SUM(W75:W78)</f>
-        <v>-4585</v>
+        <f>-396+5627-7630</f>
+        <v>-2399</v>
       </c>
       <c r="X79" s="5">
-        <f t="shared" ref="X79:AA79" si="169">SUM(X75:X78)</f>
-        <v>2938</v>
+        <f>-396+11837-9700-W79</f>
+        <v>4140</v>
       </c>
       <c r="Y79" s="5">
-        <f t="shared" si="169"/>
-        <v>6559</v>
+        <f>-396+19548-9771-X79-W79</f>
+        <v>7640</v>
       </c>
       <c r="Z79" s="5">
-        <f t="shared" si="169"/>
-        <v>-3814</v>
+        <f>1889+19548-15841-Y79-X79-W79</f>
+        <v>-3785</v>
       </c>
       <c r="AA79" s="5">
-        <f t="shared" si="169"/>
-        <v>210</v>
+        <f>-238-1052</f>
+        <v>-1290</v>
       </c>
       <c r="AB79" s="5"/>
       <c r="AC79" s="5"/>
@@ -8794,7 +8835,7 @@
     </row>
     <row r="80" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="3" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -8813,37 +8854,37 @@
       <c r="Q80" s="5"/>
       <c r="R80" s="5"/>
       <c r="S80" s="5">
-        <v>-36</v>
+        <v>27</v>
       </c>
       <c r="T80" s="5">
-        <f>-10-S80</f>
-        <v>26</v>
+        <f>31-S80</f>
+        <v>4</v>
       </c>
       <c r="U80" s="5">
-        <f>-2-T80-S80</f>
-        <v>8</v>
+        <f>34-T80-S80</f>
+        <v>3</v>
       </c>
       <c r="V80" s="5">
-        <f>-70-U80-T80-S80</f>
-        <v>-68</v>
+        <f>0-U80-T80-S80</f>
+        <v>-34</v>
       </c>
       <c r="W80" s="5">
-        <v>85</v>
+        <v>-261</v>
       </c>
       <c r="X80" s="5">
-        <f>-44-W80</f>
-        <v>-129</v>
+        <f>-276-W80</f>
+        <v>-15</v>
       </c>
       <c r="Y80" s="5">
-        <f>-95-X80-W80</f>
-        <v>-51</v>
+        <f>-299-X80-W80</f>
+        <v>-23</v>
       </c>
       <c r="Z80" s="5">
-        <f>124-Y80-X80-W80</f>
-        <v>219</v>
+        <f>1092-Y80-X80-W80</f>
+        <v>1391</v>
       </c>
       <c r="AA80" s="5">
-        <v>27</v>
+        <v>1855</v>
       </c>
       <c r="AB80" s="5"/>
       <c r="AC80" s="5"/>
@@ -8864,7 +8905,7 @@
     </row>
     <row r="81" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
@@ -8883,40 +8924,40 @@
       <c r="Q81" s="5"/>
       <c r="R81" s="5"/>
       <c r="S81" s="5">
-        <f>+S79+S80+S73+S68</f>
-        <v>1848</v>
+        <f>SUM(S77:S80)</f>
+        <v>-3528</v>
       </c>
       <c r="T81" s="5">
-        <f>+T79+T80+T73+T68</f>
-        <v>-3369</v>
+        <f>SUM(T77:T80)</f>
+        <v>-2289</v>
       </c>
       <c r="U81" s="5">
-        <f>+U79+U80+U73+U68</f>
-        <v>1237</v>
+        <f>SUM(U77:U80)</f>
+        <v>-2463</v>
       </c>
       <c r="V81" s="5">
-        <f>+V79+V80+V73+V68</f>
-        <v>973</v>
+        <f>SUM(V77:V80)</f>
+        <v>-2274</v>
       </c>
       <c r="W81" s="5">
-        <f>+W79+W80+W73+W68</f>
-        <v>162</v>
+        <f>SUM(W77:W80)</f>
+        <v>-4585</v>
       </c>
       <c r="X81" s="5">
-        <f t="shared" ref="X81:AA81" si="170">+X79+X80+X73+X68</f>
-        <v>325</v>
+        <f t="shared" ref="X81:AA81" si="167">SUM(X77:X80)</f>
+        <v>2938</v>
       </c>
       <c r="Y81" s="5">
-        <f t="shared" si="170"/>
-        <v>6465</v>
+        <f t="shared" si="167"/>
+        <v>6559</v>
       </c>
       <c r="Z81" s="5">
-        <f t="shared" si="170"/>
-        <v>-6620</v>
+        <f t="shared" si="167"/>
+        <v>-3814</v>
       </c>
       <c r="AA81" s="5">
-        <f t="shared" si="170"/>
-        <v>-341</v>
+        <f t="shared" si="167"/>
+        <v>210</v>
       </c>
       <c r="AB81" s="5"/>
       <c r="AC81" s="5"/>
@@ -8935,6 +8976,149 @@
       <c r="AQ81" s="5"/>
       <c r="AR81" s="5"/>
     </row>
+    <row r="82" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="5"/>
+      <c r="R82" s="5"/>
+      <c r="S82" s="5">
+        <v>-36</v>
+      </c>
+      <c r="T82" s="5">
+        <f>-10-S82</f>
+        <v>26</v>
+      </c>
+      <c r="U82" s="5">
+        <f>-2-T82-S82</f>
+        <v>8</v>
+      </c>
+      <c r="V82" s="5">
+        <f>-70-U82-T82-S82</f>
+        <v>-68</v>
+      </c>
+      <c r="W82" s="5">
+        <v>85</v>
+      </c>
+      <c r="X82" s="5">
+        <f>-44-W82</f>
+        <v>-129</v>
+      </c>
+      <c r="Y82" s="5">
+        <f>-95-X82-W82</f>
+        <v>-51</v>
+      </c>
+      <c r="Z82" s="5">
+        <f>124-Y82-X82-W82</f>
+        <v>219</v>
+      </c>
+      <c r="AA82" s="5">
+        <v>27</v>
+      </c>
+      <c r="AB82" s="5"/>
+      <c r="AC82" s="5"/>
+      <c r="AD82" s="5"/>
+      <c r="AE82" s="5"/>
+      <c r="AF82" s="5"/>
+      <c r="AG82" s="5"/>
+      <c r="AH82" s="5"/>
+      <c r="AI82" s="5"/>
+      <c r="AJ82" s="5"/>
+      <c r="AK82" s="5"/>
+      <c r="AL82" s="5"/>
+      <c r="AM82" s="5"/>
+      <c r="AO82" s="5"/>
+      <c r="AP82" s="5"/>
+      <c r="AQ82" s="5"/>
+      <c r="AR82" s="5"/>
+    </row>
+    <row r="83" spans="2:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
+      <c r="R83" s="5"/>
+      <c r="S83" s="5">
+        <f>+S81+S82+S75+S70</f>
+        <v>1848</v>
+      </c>
+      <c r="T83" s="5">
+        <f>+T81+T82+T75+T70</f>
+        <v>-3369</v>
+      </c>
+      <c r="U83" s="5">
+        <f>+U81+U82+U75+U70</f>
+        <v>1237</v>
+      </c>
+      <c r="V83" s="5">
+        <f>+V81+V82+V75+V70</f>
+        <v>973</v>
+      </c>
+      <c r="W83" s="5">
+        <f>+W81+W82+W75+W70</f>
+        <v>162</v>
+      </c>
+      <c r="X83" s="5">
+        <f t="shared" ref="X83:AA83" si="168">+X81+X82+X75+X70</f>
+        <v>325</v>
+      </c>
+      <c r="Y83" s="5">
+        <f t="shared" si="168"/>
+        <v>6465</v>
+      </c>
+      <c r="Z83" s="5">
+        <f t="shared" si="168"/>
+        <v>-6620</v>
+      </c>
+      <c r="AA83" s="5">
+        <f t="shared" si="168"/>
+        <v>-341</v>
+      </c>
+      <c r="AB83" s="5"/>
+      <c r="AC83" s="5"/>
+      <c r="AD83" s="5"/>
+      <c r="AE83" s="5"/>
+      <c r="AF83" s="5"/>
+      <c r="AG83" s="5"/>
+      <c r="AH83" s="5"/>
+      <c r="AI83" s="5"/>
+      <c r="AJ83" s="5"/>
+      <c r="AK83" s="5"/>
+      <c r="AL83" s="5"/>
+      <c r="AM83" s="5"/>
+      <c r="AO83" s="5"/>
+      <c r="AP83" s="5"/>
+      <c r="AQ83" s="5"/>
+      <c r="AR83" s="5"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{9063304A-9B64-48AF-9309-873C7B521AD3}"/>
